--- a/research/brics_universities/output/BRICS_universities_China_pilot.xlsx
+++ b/research/brics_universities/output/BRICS_universities_China_pilot.xlsx
@@ -664,24 +664,24 @@
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="45" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="55" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="24" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -772,92 +772,92 @@
       </c>
       <c r="R1" s="3" t="inlineStr">
         <is>
-          <t>Секретарь парткома</t>
+          <t>Рейтинг QS</t>
         </is>
       </c>
       <c r="S1" s="3" t="inlineStr">
         <is>
-          <t>Рейтинг QS</t>
+          <t>Рейтинг THE</t>
         </is>
       </c>
       <c r="T1" s="3" t="inlineStr">
         <is>
-          <t>Рейтинг THE</t>
+          <t>Национальный рейтинг</t>
         </is>
       </c>
       <c r="U1" s="3" t="inlineStr">
         <is>
-          <t>Национальный рейтинг</t>
+          <t>Запущено КА (спутников)</t>
         </is>
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
-          <t>Запущено КА (спутников)</t>
+          <t>Названия запущенных КА (год)</t>
         </is>
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>Названия запущенных КА (год)</t>
+          <t>КА в разработке</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
         <is>
-          <t>КА в разработке</t>
+          <t>Наземная станция</t>
         </is>
       </c>
       <c r="Y1" s="3" t="inlineStr">
         <is>
-          <t>Наземная станция</t>
+          <t>Космические подразделения</t>
         </is>
       </c>
       <c r="Z1" s="3" t="inlineStr">
         <is>
-          <t>Космические подразделения</t>
+          <t>Партнёрства в космической сфере</t>
         </is>
       </c>
       <c r="AA1" s="3" t="inlineStr">
         <is>
-          <t>Партнёрства в космической сфере</t>
+          <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
       <c r="AB1" s="3" t="inlineStr">
         <is>
-          <t>Санкционные / ограничительные списки (США)</t>
+          <t>Космический индекс (0–100)</t>
         </is>
       </c>
       <c r="AC1" s="3" t="inlineStr">
         <is>
-          <t>Космический индекс (0–100)</t>
+          <t>Волна рассылки</t>
         </is>
       </c>
       <c r="AD1" s="3" t="inlineStr">
         <is>
-          <t>Волна рассылки</t>
+          <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
       <c r="AE1" s="3" t="inlineStr">
         <is>
-          <t>Проверка домена e-mail (MX)</t>
+          <t>Достоверность</t>
         </is>
       </c>
       <c r="AF1" s="3" t="inlineStr">
         <is>
-          <t>Достоверность</t>
+          <t>Примечания</t>
         </is>
       </c>
       <c r="AG1" s="3" t="inlineStr">
         <is>
-          <t>Примечания</t>
+          <t>Источники</t>
         </is>
       </c>
       <c r="AH1" s="3" t="inlineStr">
         <is>
-          <t>Источники</t>
+          <t>Дата проверки</t>
         </is>
       </c>
       <c r="AI1" s="3" t="inlineStr">
         <is>
-          <t>Дата проверки</t>
+          <t>Секретарь парткома (справочно, Китай)</t>
         </is>
       </c>
     </row>
@@ -950,79 +950,74 @@
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>Qiu Xin (裘新)</t>
+          <t>QS2027: 26</t>
         </is>
       </c>
       <c r="S2" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 26</t>
+          <t>THE2027: 38</t>
         </is>
       </c>
       <c r="T2" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 38</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 5</t>
         </is>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>• Fudan Information Star / Jiguang constellation-01 (复旦信息星, 2024-05-31, Ceres-1)
 • Fudan-1 / Lancang-Mekong Future Star (复旦一号/澜湄未来星, ~50 kg, 2024-09)
 • Fuyao (复遥号, 2024-11-11)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>• School of Information Science &amp; Engineering says its next technology test satellite is in preparation (2024)
 • No name published</t>
         </is>
       </c>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>Fudan University satellite ground station (复旦大学卫星地面站) receives real-time Fuyao data; bands not published</t>
+        </is>
+      </c>
       <c r="Y2" s="4" t="inlineStr">
-        <is>
-          <t>Fudan University satellite ground station (复旦大学卫星地面站) receives real-time Fuyao data; bands not published</t>
-        </is>
-      </c>
-      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>• School of Information Science and Engineering (Jin Yaqiu group, space-borne remote sensing/laser comms)
 • Department of Nuclear Science and Technology (Fudan-1 solar UV spectrometer)
 • Lancang-Mekong Youth Astronomical Science Research Centre (2025)</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>• Fudan-1 co-developed with Shanghai Academy of Spaceflight Technology (CASC 8th Academy) / Shanghai Aerospace Space Technology Co
 • Fudan-1 data shared with the six Lancang-Mekong (LMC) countries
 • Jiguang constellation with HiStarlink (laser communications) and Shanghai Dianji University</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="AB2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AC2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD2" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE2" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF2" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• 3 КА в 2024, собственная наземная станция, опыт международного проекта Ланьцан–Меконг — сильный партнёр
 • Fudan-1 и Fuyao созданы совместно с промышленностью (SAST)
@@ -1030,7 +1025,7 @@
 • Адресат: ogp@fudan.edu.cn указан на странице контактов как ящик «综合业务» (общая работа отдела). Личный e-mail начальника: lalu@fudan.edu.cn — можно поставить в копию</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fudan.edu.cn/448/list.htm
 • Https://www.fudan.edu.cn/en/Contact_931/list.htm
@@ -1045,9 +1040,14 @@
 • Https://ogp.fudan.edu.cn/16079/list.htm</t>
         </is>
       </c>
+      <c r="AH2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Qiu Xin (裘新)</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,23 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>Zhang Yunming (张云明)</t>
+          <t>QS2027: 425</t>
         </is>
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 425</t>
+          <t>THE2027: =224</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =224</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 23</t>
         </is>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>• Aoxiang Zhixing / Star of Aoxiang, first 12U CubeSat (2016)
 • Xingyun Shiyan-1 / XY-S1 (2017)
@@ -1176,51 +1171,51 @@
 • Qinling-01 &amp; Qinling-02 (2026, 150 kg sub-metre imaging)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>Qinling Constellation planned at 36 satellites (visible, hyperspectral, SAR) for Shaanxi province</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>• School of Astronautics
 • School of Aeronautics
 • Micro-satellite team (Aoxiang series)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• Macau Science-1 with Macau University of Science and Technology and CAST DFH Satellite Co
 • QB50 (Aoxiang-1)
 • IAF member since 2019</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE3" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF3" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Новый секретарь парткома Чжан Юньмин (экс-замминистра MIIT) с мая 2026
 • Телефон и e-mail: отдел международного сотрудничества (г-жа Чэн Инь); альтернативно fao@nwpu.edu.cn, +86-29-88492267
@@ -1228,7 +1223,7 @@
 • Адресат: wgzj@nwpu.edu.cn (wgzj = «иностранные специалисты») — адрес сектора иностранных специалистов, контактное лицо г-жа Чэн Инь (Cheng Yin, тел. 88492812): https://en.nwpu.edu.cn/EnglishNew/index/contactus.htm. Сейчас официальный адрес отдела — nwpuge@nwpu.edu.cn. Сайт защищён от ботов, страница прочитана через WebFetch (пересказ). Замначальника отдела — Ли Цзывэй (李自伟) и Чэнь Цзюнь (陈俊)</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.acabridge.cn/yxxw/gxrs/202605/t20260509_2733421.shtml
 • Https://en.nwpu.edu.cn/EnglishNew/index/contactus.htm
@@ -1245,9 +1240,14 @@
 • Https://guoji.nwpu.edu.cn/jggk/lxwm.htm</t>
         </is>
       </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Zhang Yunming (张云明)</t>
         </is>
       </c>
     </row>
@@ -1345,46 +1345,41 @@
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>Liu Chenggong (刘承功)</t>
+          <t>QS2027: 258</t>
         </is>
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 258</t>
+          <t>THE2027: =205</t>
         </is>
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =205</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 13</t>
         </is>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>• TianQin-1 (天琴一号, technology test satellite co-developed with HUST and DFH Satellite Co., 2019)
 • Yixian-A (逸仙-A, student 3U CubeSat with wooden panels, 2025
 • First attempt lost in a 2024 launch failure)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>• TianQin programme: Step 2 dual-satellite laser-interferometry test (in progress)
 • Step 3 three-satellite TianQin gravitational-wave observatory (~100,000 km orbit, target ~2035)</t>
         </is>
       </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>TianQin Center operates a lunar/satellite laser ranging station (Zhuhai) and ground stations for satellite data collection (bands not published)</t>
+        </is>
+      </c>
       <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>TianQin Center operates a lunar/satellite laser ranging station (Zhuhai) and ground stations for satellite data collection (bands not published)</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics (Shenzhen campus)
 • TianQin Research Center for Gravitational Physics (MOE Key Lab
@@ -1394,7 +1389,7 @@
 • School of Atmospheric Sciences</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>• CNSA (TianQin-1 accepted by CNSA, rated 'excellent'
 • TianQin Center hosts a CNSA research centre)
@@ -1402,26 +1397,26 @@
 • HUST</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
+      <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE4" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF4" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Смена руководства: секретарь парткома Лю Чэнгун (ноябрь 2025), президент Тан Хунъу (июль 2026); собственная страница вуза устарела
 • Входит в Unverified List (UVL) Минторга США — не Entity List
@@ -1430,7 +1425,7 @@
 • Адресат исправлен: с июля 2026 президент — Тан Хунъу (Гао Сун перешёл в PKU)</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.news.cn/politics/20260703/0805d89b4e584a0682a9ed20f1a5291f/c.html
 • Https://edu.cnr.cn/dj/20251120/t20251120_527435649.shtml
@@ -1448,9 +1443,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Liu Chenggong (刘承功)</t>
         </is>
       </c>
     </row>
@@ -1544,46 +1544,41 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>Shu Gequn (舒歌群)</t>
+          <t>QS2027: 134</t>
         </is>
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 134</t>
+          <t>THE2027: =51</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =51</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 7</t>
         </is>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>• Micius / QUESS (墨子号, world's first quantum science satellite, USTC-led, 2016)
 • Jinan-1 (济南一号, quantum micro-nano satellite, led by Hefei National Laboratory with USTC and Jinan Institute of Quantum Technology, 2022)</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>• MERLIS 12U CubeSat (mm-wave satcom/UHD video
 • Listed as not launched on nanosats.eu)
 • Planned quantum micro-nano satellite constellation</t>
         </is>
       </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>Portable/mobile quantum optical ground stations (&lt;100 kg) used with Jinan-1 for real-time satellite-to-ground QKD (incl. link to Stellenbosch, South Africa)</t>
+        </is>
+      </c>
       <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>Portable/mobile quantum optical ground stations (&lt;100 kg) used with Jinan-1 for real-time satellite-to-ground QKD (incl. link to Stellenbosch, South Africa)</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>• School of Earth and Space Sciences
 • CAS Key Laboratory of Quantum Information
@@ -1591,7 +1586,7 @@
 • Department of Modern Physics / Deep space &amp; astrophysics groups</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>• Chinese Academy of Sciences (USTC is a CAS university
 • Micius was a CAS Strategic Priority project)
@@ -1601,26 +1596,26 @@
 • Stellenbosch University (South Africa, BRICS quantum link)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD5" s="5" t="inlineStr">
+      <c r="AC5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE5" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF5" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• В Entity List США входит лаборатория при USTC (Hefei National Laboratory), сам вуз — нет
 • Президент Чан Цзинь с октября 2024; Пань Цзяньвэй руководит квантовыми спутниками
@@ -1629,7 +1624,7 @@
 • Адресат: oic@ustc.edu.cn указан на oic.ustc.edu.cn; в шапке сайта как «通联邮箱» указан также fanjiangqi@ustc.edu.cn. Личный адрес начальника: qukun@ustc.edu.cn</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ustc.edu.cn/xxgk/xrld.htm
 • Https://news.ustc.edu.cn/info/1055/89173.htm
@@ -1647,9 +1642,14 @@
 • Https://oic.ustc.edu.cn/%e5%85%b3%e4%ba%8e%e6%88%91%e4%bb%ac/%e4%ba%ba%e5%91%98%e4%bf%a1%e6%81%af/</t>
         </is>
       </c>
+      <c r="AH5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Shu Gequn (舒歌群)</t>
         </is>
       </c>
     </row>
@@ -1740,28 +1740,23 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>Zhu Kongjun (朱孔军)</t>
+          <t>QS2027: 165</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 165</t>
+          <t>THE2027: =121</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =121</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 8</t>
         </is>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="U6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>• Luojia-1 01 (珞珈一号01星, night-light 6U, 2018)
 • Qimingxing-1 (启明星一号, student microsat, 2022)
@@ -1771,18 +1766,18 @@
 • Luojia-4 01 'People's Health' (珞珈四号01星, medical remote sensing, 2024)</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>• Dongfang Huiyan (Oriental SmartEye) intelligent remote-sensing constellation with Yantai municipality (phased to 200+ satellites by 2030
 • First high-res satellite launched Feb 2024, WHU as chief scientist/designer)</t>
         </is>
       </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>Wuhan University Remote Sensing Satellite Ground Station (operational Dec 2012; 13 m X/S dual-band and 12 m Ka/X/S tri-band TT&amp;C/data-receiving systems; master station for all Luojia satellites; supported Chang'e-3/5 and Tianwen-1 tracking)</t>
+        </is>
+      </c>
       <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>Wuhan University Remote Sensing Satellite Ground Station (operational Dec 2012; 13 m X/S dual-band and 12 m Ka/X/S tri-band TT&amp;C/data-receiving systems; master station for all Luojia satellites; supported Chang'e-3/5 and Tianwen-1 tracking)</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>• State Key Laboratory of Information Engineering in Surveying, Mapping and Remote Sensing (LIESMARS)
 • School of Remote Sensing and Information Engineering
@@ -1791,7 +1786,7 @@
 • GNSS Research Center</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>• CAST / DFH Satellite Co. (Luojia-3 01 co-design)
 • CASIC (Kuaizhou launches)
@@ -1799,26 +1794,26 @@
 • Support to CNSA lunar/Mars missions via ground station</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD6" s="5" t="inlineStr">
+      <c r="AC6" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE6" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF6" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Сильнейший в выборке оператор спутников и ДЗЗ, собственная наземная станция Ka/X/S — приоритетный партнёр
 • Секретарь парткома Чжу Кунцзюнь с сентября 2025
@@ -1828,7 +1823,7 @@
 • Адресат: Адрес fao@whu.edu.cn взят с en.whu.edu.cn/Contact_Us/Office_of_International_Affairs.htm (Section of General Affairs). Страница руководства обновлена 2026-09-09; Дэн Хэсян руководит всей работой и курирует общий отдел</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.whu.edu.cn/xxgk/xrld.htm
 • Https://www.news.cn/politics/20250919/f203a39343a1422fbe1dcfbda5f74872/c.html
@@ -1850,9 +1845,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Zhu Kongjun (朱孔军)</t>
         </is>
       </c>
     </row>
@@ -1927,24 +1927,19 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>Xu Mei (续梅)</t>
-        </is>
-      </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
           <t>QS2027: 1001-1200</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>BCUR2026: 50</t>
         </is>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>• BUPT-Galaxy (北邮-银河号, with GalaxySpace, 2022)
 • BUPT-1 (北邮一号, 12U, Tiansuan constellation main satellite, 2023)
@@ -1953,24 +1948,24 @@
 • BUPT-4 (北邮四号, 50 kg class, with Tianyi/Spacety, 2026)</t>
         </is>
       </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>Tiansuan (天算) space-computing constellation phase 2 (reported plan of ~24 satellites)</t>
+        </is>
+      </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>Tiansuan (天算) space-computing constellation phase 2 (reported plan of ~24 satellites)</t>
+          <t>Tiansuan constellation ground segment incl. an East China (Shandong) ground station and a 'space computing cloud' ground-station service platform (bands not published)</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>Tiansuan constellation ground segment incl. an East China (Shandong) ground station and a 'space computing cloud' ground-station service platform (bands not published)</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>• Tiansuan Constellation programme (Prof. Wang Shangguang team, State Key Lab of Networking and Switching Technology)
 • BUPT Shenzhen Research Institute
 • Space computing / satellite internet research groups</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>• Changsha Tianyi Research Institute (Spacety)
 • GalaxySpace
@@ -1981,26 +1976,26 @@
 • Yantai University</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Entity List США</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AB7" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="inlineStr"/>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
       <c r="AF7" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Сайты вуза блокировали запросы — контакты не подтверждены; по поиску: межд. отдел +86-10-62281949, admissions@bupt.edu.cn
 • В Entity List США
@@ -2009,7 +2004,7 @@
 • Адресат: Все сайты BUPT (www, io.bupt.edu.cn, english) отдают 412 (антибот-защита), страницы открыть не удалось. По результатам поиска начальником может быть Чэнь Янь (陈岩), но это не подтверждено открытой страницей. Официальный адрес отдела для партнёрств не найден (найдены только адреса приёма иностранных студентов)</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Https://news.qq.com/rain/a/20260920V0D5QV00
 • Https://peking.bjd.com.cn/content/s6ab274fde4b0e42f8f00ab63.html
@@ -2026,9 +2021,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Xu Mei (续梅)</t>
         </is>
       </c>
     </row>
@@ -2126,73 +2126,68 @@
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>Cheng Jianping (程建平)</t>
+          <t>QS2027: 237</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 237</t>
+          <t>THE2027: 125</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 125</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 19</t>
         </is>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="U8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>• BNU-1 / Jingshi-1 polar-observation smallsat (京师一号, ~16 kg, 2019-09-12
 • Built for BNU by Shenzhen Aerospace Dongfanghong HIT Satellite)
 • MuDuo-1A and MuDuo-1B instant remote-sensing constellation (木铎一号, 2026-08-25)</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Further expansion of the MuDuo (木铎) satellite network constellation</t>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Geographical Science
 • Institute of Global Change and Earth System Science
 • Frontier Interdisciplinary Research Institute for Satellite Applications (卫星应用前沿交叉研究院)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>• BNU-1 co-funded by Ministry of Science and Technology
 • Built by Shenzhen Aerospace Dongfanghong HIT Satellite Ltd (CAST/HIT)</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
+      <c r="AC8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE8" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF8" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Пользователь и оператор спутников ДЗЗ: BNU-1 (полярные наблюдения) и группировка MuDuo (2026)
 • Общий e-mail — адрес новостного центра
@@ -2200,7 +2195,7 @@
 • Адресат: Исходный oiec3@bnu.edu.cn принадлежит Fang Shunji (方顺姬) — сотруднику по студенческим выездным обменам (Азия, Африка); для приглашения к институциональному партнёрству не подходит. Liu Min отвечает за межвузовские обмены и проекты сотрудничества. Начальник отдела — Teng Jun (滕珺, tengjun1983@bnu.edu.cn) — рекомендуется в копию</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bnu.edu.cn/xxgk/xrld/index.htm
 • Https://english.bnu.edu.cn/dblj1/contactus/index.htm
@@ -2213,9 +2208,14 @@
 • Https://oiec.bnu.edu.cn/gywm/lxwm/index.htm</t>
         </is>
       </c>
+      <c r="AH8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Cheng Jianping (程建平)</t>
         </is>
       </c>
     </row>
@@ -2309,28 +2309,23 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>Ren Shaobo (任少波)</t>
+          <t>QS2027: 47</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 47</t>
+          <t>THE2027: 34</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 34</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 3</t>
         </is>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>• ZDPS-1 / Pixing-1 MEMS-Pico (2007, no signal)
 • ZDPS-1A x2 / Pixing-1A (2010)
@@ -2340,44 +2335,44 @@
 • WJ-1B, Oman's first satellite (2024)</t>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <t>In Aug 2020 ZJU said it planned ~20 more satellites within a year (status not verified)</t>
         </is>
       </c>
-      <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr"/>
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics
 • Micro-Satellite Research Center (School of Information and Electronic Engineering)
 • Spacecraft intelligent technology team</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr">
         <is>
           <t>WJ-1B built for Oman (Oman's first satellite), assembly/test support from CAST 5th Academy</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AD9" s="5" t="inlineStr">
+      <c r="AC9" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE9" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF9" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Телефон/e-mail: Office of Global Engagement (кампус Цзыцзиньган)
 • 8 КА — по перечисленным запускам; вероятно больше, требуется проверка
@@ -2385,7 +2380,7 @@
 • Адресат: Личный адрес начальника — jyleung@zju.edu.cn. В Офисе по сотрудничеству (合作交流办公室) Африку и Латинскую Америку курирует Сунь Мо (孙墨, mosun@zju.edu.cn), Россию — Ху Линьюань (胡临远, jo.huly@zju.edu.cn), Азию — Чжан Чуюнь (张楚韵, zhangchuyun@zju.edu.cn). Их стоит поставить в копию</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Https://www.zju.edu.cn/xrld/list.htm
 • Https://www.zju.edu.cn/2025/0328/c76679a3032574/page.htm
@@ -2401,9 +2396,14 @@
 • Http://www.ir.zju.edu.cn/69632/list.htm</t>
         </is>
       </c>
+      <c r="AH9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Ren Shaobo (任少波)</t>
         </is>
       </c>
     </row>
@@ -2497,73 +2497,68 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>Yang Zhenbin (杨振斌)</t>
+          <t>QS2027: 36</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 36</t>
+          <t>THE2027: 39</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 39</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 4</t>
         </is>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>• APSCO-SSS-2A / SJTU Siyuan-1 (思源一号, 3U, 2021)
 • ICUBE-Q / SJTU Siyuan-2 (思源二号, lunar-orbit CubeSat co-developed with Pakistan's IST, carried by Chang'e-6, 2024)</t>
         </is>
       </c>
-      <c r="X10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>Ground ops capability at Intelligent Satellite Technology Center (team ran first-signal monitoring for SSS-2A at a Kashgar test station); no dedicated university station with bands verified</t>
+        </is>
+      </c>
       <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>Ground ops capability at Intelligent Satellite Technology Center (team ran first-signal monitoring for SSS-2A at a Kashgar test station); no dedicated university station with bands verified</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics
 • Intelligent Satellite Technology Center (SSTC, led by IAA academician Wu Shufan)
 • SJTU–Shanghai Institute of Satellite Engineering joint graduate training base</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>• APSCO (Student Small Satellite project SSS-2A)
 • CNSA Chang'e-6 international payload (ICUBE-Q with Pakistan IST/SUPARCO side)
 • Shanghai Institute of Satellite Engineering (CASC/SAST) joint training base</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="n">
+      <c r="AA10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AD10" s="5" t="inlineStr">
+      <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD10" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE10" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF10" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Команда также участвовала в STU-2 (3 кубсата, 2015) и SDS-1, но они велись другими организациями — не учтены
 • Общий e-mail не опубликован; использовать международный отдел globalsjtu@sjtu.edu.cn
@@ -2571,7 +2566,7 @@
 • Адресат: globalsjtu@sjtu.edu.cn указан как общий ящик отдела на global.sjtu.edu.cn/about/contact; личный адрес начальника: htyin@sjtu.edu.cn</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Https://dzb.sjtu.edu.cn/Data/List/xzjs
 • Https://news.qq.com/rain/a/20260914A0DOCS00
@@ -2589,9 +2584,14 @@
 • Https://global.sjtu.edu.cn/about/organization</t>
         </is>
       </c>
+      <c r="AH10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Yang Zhenbin (杨振斌)</t>
         </is>
       </c>
     </row>
@@ -2685,42 +2685,37 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>Liu Jie (刘杰)</t>
+          <t>QS2027: =677</t>
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>QS2027: =677</t>
+          <t>THE2022: 801-1000 (not listed in later editions)</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>THE2022: 801-1000 (not listed in later editions)</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 56</t>
         </is>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>• Dizhi-1 / Geology-1 (地质一号, hyperspectral smallsat, co-led with China Aero Geophysical Survey and Remote Sensing Center for Natural Resources
 • Chief engineer Prof. Wang Lizhe) (17 May 2025)
 • Dianjian-1 (电建一号, ~300 kg X-band SAR, led by PowerChina Chengdu Institute, CUG co-developer) (15 May 2026)</t>
         </is>
       </c>
-      <c r="X11" s="4" t="inlineStr">
+      <c r="W11" s="4" t="inlineStr">
         <is>
           <t>• Dizhi-2 (地质二号) hyperspectral satellite (planned
 • Part of a hyperspectral geological constellation concept)</t>
         </is>
       </c>
-      <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="inlineStr">
+      <c r="X11" s="4" t="inlineStr"/>
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>• School of Geophysics and Geomatics / Space Information (地球物理与空间信息学院)
 • School of Earth and Planetary Sciences (地球与行星科学学院)
@@ -2728,7 +2723,7 @@
 • School of Computer Science</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="inlineStr">
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>• China Aero Geophysical Survey and Remote Sensing Center for Natural Resources (MNR/China Geological Survey)
 • Spacety (天仪研究院)
@@ -2737,26 +2732,26 @@
 • PowerChina Chengdu Engineering Corp</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="AD11" s="5" t="inlineStr">
+      <c r="AC11" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE11" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF11" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Самая активная космическая программа в своей группе: Dizhi-1 (2025), Dianjian-1 (2026, совместно с PowerChina)
 • Dizhi-2 в планах
@@ -2764,7 +2759,7 @@
 • Адресат: Адрес cug_global@cug.edu.cn на сайте управления (там только телефоны) не найден — владелец ящика определён по смыслу. Стратегические соглашения ведёт Офис программ совместного обучения (中外合作办学办公室, зам. начальника Fan Luwei 范陆薇)</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cug.edu.cn/xxgk/xrld.htm
 • Https://gjhzc.cug.edu.cn/
@@ -2782,9 +2777,14 @@
 • Https://gjhzc.cug.edu.cn/jgsz/bmld.htm</t>
         </is>
       </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Liu Jie (刘杰)</t>
         </is>
       </c>
     </row>
@@ -2878,71 +2878,66 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>Xiang Changle (项昌乐)</t>
+          <t>QS2027: 463</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 463</t>
+          <t>THE2027: 326–350</t>
         </is>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 326–350</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 28</t>
         </is>
       </c>
-      <c r="V12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>Dalian-1 Lianli (大连1号—连理卫星, 12U CubeSat, launched on Tianzhou-6 2023, released from orbit Jan 2024)</t>
+        </is>
+      </c>
       <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>Dalian-1 Lianli (大连1号—连理卫星, 12U CubeSat, launched on Tianzhou-6 2023, released from orbit Jan 2024)</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>• 12U exoplanet CubeSat concept (Proxima b study
 • Listed as not launched on nanosats.eu)</t>
         </is>
       </c>
-      <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="X12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics (Faculty of Vehicle Engineering and Mechanics)
 • Micro-nano Satellite and Deep Space Exploration team (Prof. Yu Xiaozhou)</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="inlineStr">
+      <c r="Z12" s="4" t="inlineStr">
         <is>
           <t>• China Manned Space Agency (satellite flown via Tianzhou-6 cargo ship)
 • OpenHarmony / OpenAtom Foundation (satellite OS)</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="n">
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD12" s="5" t="inlineStr">
+      <c r="AC12" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE12" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF12" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Президент Гао Сян с октября 2025
 • Международный отдел: dutfao@dlut.edu.cn, +86-411-84706354, факс +86-411-84707983
@@ -2950,7 +2945,7 @@
 • Адресат: dutfao@dlut.edu.cn указан в подвале сайта отдела dutdice.dlut.edu.cn. Личный адрес начальника: wangjue@dlut.edu.cn</t>
         </is>
       </c>
-      <c r="AH12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Https://www.dlut.edu.cn/xxgk/xrld.htm
 • Http://www.news.cn/politics/20251021/d10e8782ff66432aa79cf5eb6f5f7d96/c.html
@@ -2968,9 +2963,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Xiang Changle (项昌乐)</t>
         </is>
       </c>
     </row>
@@ -3068,28 +3068,23 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>Chen Jie (陈杰)</t>
+          <t>QS2027: 190</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 190</t>
+          <t>THE2027: 96</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 96</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 12</t>
         </is>
       </c>
-      <c r="V13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>• HIT reports 46 satellites developed and launched as of Jul 2026
 • Named examples: Shiyan-1 (2004)
@@ -3105,16 +3100,16 @@
 • Zidingxiang-3 / Lilac-3 (2026)</t>
         </is>
       </c>
+      <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="Y13" s="4" t="inlineStr">
         <is>
           <t>• School of Astronautics
 • School of Aeronautics
 • Lilac (Zidingxiang) student micro-nano satellite team</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="inlineStr">
+      <c r="Z13" s="4" t="inlineStr">
         <is>
           <t>• Shijian-26 co-developed with CAST's DFH Satellite Co. and CAS Changchun Institute of Optics (CIOMP)
 • Longjiang-1/2 flew with Chang'e-4 relay mission (CNSA lunar programme)
@@ -3123,31 +3118,31 @@
 • APRU member</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AA13" s="4" t="inlineStr">
         <is>
           <t>Entity List США (с May 2020)
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="n">
+      <c r="AB13" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD13" s="5" t="inlineStr">
+      <c r="AC13" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE13" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF13" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>• Крупнейший вузовский разработчик спутников в Китае: 46 запущенных КА по данным вуза (июль 2026), включая совместные национальные аппараты; полный перечень не опубликован
 • Телефон: отдел управления международным образованием
@@ -3156,7 +3151,7 @@
 • Адресат: Должность «начальник» (部长) на странице не указана, департаментом руководит исполнительный замначальника У Цзянь (jian.wu@hit.edu.cn). В HIT есть отдельный Офис по международным организациям и делам БРИКС (国际组织和金砖事务办公室), руководитель — Сюй Лу (徐璐, xulu@hit.edu.cn): http://international.hit.edu.cn/gjzzhjzswbgs/list.htm. Рекомендуем поставить её в копию</t>
         </is>
       </c>
-      <c r="AH13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>• Https://www.hit.edu.cn/11542/list.htm
 • Https://en.hit.edu.cn/
@@ -3178,9 +3173,14 @@
 • Http://international.hit.edu.cn/16710/list.htm</t>
         </is>
       </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Chen Jie (陈杰)</t>
         </is>
       </c>
     </row>
@@ -3274,80 +3274,75 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>Liu Bo (刘波)</t>
+          <t>QS2027: 307</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 307</t>
+          <t>THE2027: =191</t>
         </is>
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =191</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 9</t>
         </is>
       </c>
-      <c r="V14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W14" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>• TianQin-1 (天琴一号, 2019-12-20
 • Co-developed with Sun Yat-sen University and DFH Satellite Co
 • HUST built the inertial sensing payload)</t>
         </is>
       </c>
-      <c r="X14" s="4" t="inlineStr">
+      <c r="W14" s="4" t="inlineStr">
         <is>
           <t>• TianQin space gravitational-wave constellation (3 satellites ~100,000 km orbit, ~2035
 • SYSU-led programme proposed by HUST academician Luo Jun)</t>
         </is>
       </c>
-      <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr">
         <is>
           <t>• Institute of Digital Aerospace Technology (数字空天技术研究所, est. 2023)
 • TianQin research centre / precision gravitational measurement</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="inlineStr">
+      <c r="Z14" s="4" t="inlineStr">
         <is>
           <t>• TianQin-1 with CAST subsidiary DFH Satellite Co. and Sun Yat-sen University
 • CNSA acceptance of TianQin-1</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="n">
+      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD14" s="5" t="inlineStr">
+      <c r="AC14" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE14" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>• Участие в КА — полезная нагрузка (инерциальный датчик) на TianQin-1; программу TianQin ведёт SYSU
 • Единого международного e-mail нет; адреса сотрудников по регионам
 • Адресат: Начальник управления — Chen Jie (陈洁, 处长). Россия и ЮАР относятся к офису Европы и Африки (курирует зам. начальника Jiang Jing, 江静). Общий ящик управления: international@hust.edu.cn — разумно поставить в копию</t>
         </is>
       </c>
-      <c r="AH14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>• Https://www.hust.edu.cn/xxgk/xrld.htm
 • Https://www.hust.edu.cn/
@@ -3361,9 +3356,14 @@
 • Http://oia.hust.edu.cn/gywm/bmld.htm</t>
         </is>
       </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Liu Bo (刘波)</t>
         </is>
       </c>
     </row>
@@ -3461,28 +3461,23 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>Qiu Yong (邱勇)</t>
+          <t>QS2027: 14</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 14</t>
+          <t>THE2027: 11</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 11</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 1</t>
         </is>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="W15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>• Tsinghua-1 (2000, with SSTL &amp; CASIC)
 • NS-1 / Naxing-1 (2004)
@@ -3490,41 +3485,41 @@
 • Tsinghua Science Satellite (2020, gravity/atmosphere)</t>
         </is>
       </c>
+      <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr">
+      <c r="Y15" s="4" t="inlineStr">
         <is>
           <t>• School of Aerospace Engineering
 • Space Technology Center (宇航技术研究中心)
 • GRID (Tiange) gamma-ray payload project</t>
         </is>
       </c>
-      <c r="AA15" s="4" t="inlineStr">
+      <c r="Z15" s="4" t="inlineStr">
         <is>
           <t>• Tsinghua-1 jointly built with CASIC and University of Surrey/SSTL (Tsinghua-Surrey microsatellite centre)
 • IAF member since 2018</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="n">
+      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD15" s="5" t="inlineStr">
+      <c r="AC15" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE15" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF15" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>• КА: 7 к сентябрю 2015 (новости вуза) + Tsinghua Science Satellite (2020) = не менее 8; возможны более поздние запуски
 • Не найден в Entity List США (список Caltech, неполный)
@@ -3532,7 +3527,7 @@
 • Адресат: liaison@ читает Офис по обменам (тел. 62781943/62783293), а общий адрес отдела и руководства — guojichu@tsinghua.edu.cn, его стоит поставить в копию. Пиньинь имени 茜 в именах обычно читается как Qian, на сайте латиницей не указан</t>
         </is>
       </c>
-      <c r="AH15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tsinghua.edu.cn/xxgk/xrld.htm
 • Https://www.tsinghua.edu.cn/en/Contact.htm
@@ -3549,9 +3544,14 @@
 • Https://www.tsinghua.edu.cn/gjhz/gywm/lxwm.htm</t>
         </is>
       </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Qiu Yong (邱勇)</t>
         </is>
       </c>
     </row>
@@ -3649,40 +3649,35 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>Ren Xiaolong (任小龙)</t>
+          <t>QS2027: 851-900</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 851-900</t>
+          <t>THE2027: 601–650</t>
         </is>
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 601–650</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 39</t>
         </is>
       </c>
-      <c r="V16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>Xidian-1 (西电一号, hyperspectral satellite, first of the Zhongxing Silk Road Sky Map constellation, co-developed with China Star Electric/Future Aerospace, 2022)</t>
+        </is>
+      </c>
       <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t>Xidian-1 (西电一号, hyperspectral satellite, first of the Zhongxing Silk Road Sky Map constellation, co-developed with China Star Electric/Future Aerospace, 2022)</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
         <is>
           <t>• Follow-on satellites of the Silk Road Sky Map (丝路天图) remote-sensing constellation (reported as planned
 • Details unverified)</t>
         </is>
       </c>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr">
+      <c r="X16" s="4" t="inlineStr"/>
+      <c r="Y16" s="4" t="inlineStr">
         <is>
           <t>• School of Aerospace Science and Technology (空间科学与技术学院, est. 2013)
 • National Key Laboratory of Antennas and Microwave Technology
@@ -3692,33 +3687,33 @@
 • Qian Xuesen Space Science talent base (with CAST Qian Xuesen Space Technology Lab)</t>
         </is>
       </c>
-      <c r="AA16" s="4" t="inlineStr">
+      <c r="Z16" s="4" t="inlineStr">
         <is>
           <t>• CAST Qian Xuesen Space Technology Laboratory (joint talent base)
 • China Star Electric Aerospace / Future Aerospace (Xidian-1)
 • CASIC Defense Technology Research &amp; Test Center (strategic cooperation, microelectronics school)</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="n">
+      <c r="AA16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="AD16" s="5" t="inlineStr">
+      <c r="AC16" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE16" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF16" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>• Исторически военный вуз связи; в Entity List не найден, но проверять при передаче технологий США
 • Общий e-mail — ящик президента (校长信箱); ящик секретаря парткома sjxx@xidian.edu.cn
@@ -3727,7 +3722,7 @@
 • Адресат: fao@xidian.edu.cn указан в подвале oice.xidian.edu.cn. Личный адрес: ylshen@mail.xidian.edu.cn</t>
         </is>
       </c>
-      <c r="AH16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>• Https://www.xidian.edu.cn/xxgk/xrld.htm
 • Http://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202505/t20250516_1190844.html
@@ -3745,9 +3740,14 @@
 • Https://oice.xidian.edu.cn/gywm/bmgk/zzjg.htm</t>
         </is>
       </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Ren Xiaolong (任小龙)</t>
         </is>
       </c>
     </row>
@@ -3841,36 +3841,31 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>Wang Yunpeng (王云鹏)</t>
+          <t>QS2027: 349</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 349</t>
+          <t>THE2027: =185</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =185</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 11</t>
         </is>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>• Beihang Kongshi-1 / BUAA Air Traffic Satellite-1 (2020, 12U, co-developed with Changsha Tianyi/Spacety)
 • APSCO Student Small Satellite SSS-1 (2021, 36 kg)</t>
         </is>
       </c>
+      <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="inlineStr">
+      <c r="Y17" s="4" t="inlineStr">
         <is>
           <t>• School of Astronautics
 • School of Aeronautic Science and Engineering
@@ -3878,7 +3873,7 @@
 • Regional Centre for Space Science and Technology Education in Asia and the Pacific (China) (RCSSTEAP, UN-affiliated, hosted by Beihang)</t>
         </is>
       </c>
-      <c r="AA17" s="4" t="inlineStr">
+      <c r="Z17" s="4" t="inlineStr">
         <is>
           <t>• APSCO (leads APSCO Student Small Satellite project
 • SSS-1 with participation of Pakistan, Peru etc.)
@@ -3887,31 +3882,31 @@
 • IAF member since 2011</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr">
+      <c r="AA17" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC17" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AD17" s="5" t="inlineStr">
+      <c r="AC17" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE17" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>• 30.09.2026 президент Ван Юньпэн назначен секретарём парткома (вместо Чжао Чанлу); на сайте он указан в обеих должностях — вероятно скорое назначение нового президента, перепроверить перед рассылкой
 • Телефон: International School (бакалавриат)
@@ -3920,7 +3915,7 @@
 • Адресат: На странице international@buaa.edu.cn указан как личный рабочий адрес начальника Бай Линь, так что письмо дойдёт адресату напрямую. К департаменту прикреплены Азиатско-Тихоокеанский региональный центр ООН по космическому образованию (Китай) и учебный центр APSCO, что тематически близко к проекту CubeSat</t>
         </is>
       </c>
-      <c r="AH17" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.buaa.edu.cn/xygk/xxld.htm
 • Https://www.sohu.com/a/1082601837_121019331
@@ -3940,9 +3935,14 @@
 • Https://global.buaa.edu.cn/gywm/zzjg.htm</t>
         </is>
       </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Wang Yunpeng (王云鹏)</t>
         </is>
       </c>
     </row>
@@ -4034,66 +4034,61 @@
           <t>President</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>Xu Huarui (徐华瑞)</t>
-        </is>
-      </c>
+      <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>BCUR2026: 86</t>
         </is>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="W18" s="4" t="inlineStr">
+      <c r="V18" s="4" t="inlineStr">
         <is>
           <t>• CXPD-01 (1U X-ray polarimetry CubeSat, 2023-06-07, Lijian-1)
 • CXPD-03 &amp; CXPD-04 (2025-05-14, with Zhejiang Lab Three-Body Computing Constellation)
 • CXPD-02 (2025-05-17, Zhuque-2E)</t>
         </is>
       </c>
-      <c r="X18" s="4" t="inlineStr">
+      <c r="W18" s="4" t="inlineStr">
         <is>
           <t>Next-generation low-energy polarisation detector for the China Space Station (POLAR-2)</t>
         </is>
       </c>
-      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="X18" s="4" t="inlineStr"/>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>School of Physical Science and Technology (物理科学与工程技术学院), CXPD collaboration lead</t>
+        </is>
+      </c>
       <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>School of Physical Science and Technology (物理科学与工程技术学院), CXPD collaboration lead</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
         <is>
           <t>• CXPD collaboration with CAS Institute of High Energy Physics, University of CAS, Central China Normal University and Beijing Institute of Spacecraft Environment Engineering (CAST)
 • Zhejiang Lab Three-Body Computing Constellation
 • POLAR-2 on China Space Station</t>
         </is>
       </c>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="n">
+      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AD18" s="5" t="inlineStr">
+      <c r="AC18" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD18" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE18" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF18" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>• Активная программа кубсатов: 4 рентгеновских поляриметра на орбите с 2023
 • Нет в рейтингах THE 2027 и QS 2027 (топ-500)
@@ -4101,7 +4096,7 @@
 • Адресат: Сайт отдела переехал на gjjl.gxu.edu.cn; gjc@gxu.edu.cn указан там как официальный e-mail отдела</t>
         </is>
       </c>
-      <c r="AH18" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>• Https://www.gxu.edu.cn/en/About_GX/Current_Administrators.htm
 • Https://www.gxu.edu.cn/en/info/1204/2095.htm
@@ -4113,9 +4108,14 @@
 • Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking</t>
         </is>
       </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Xu Huarui (徐华瑞)</t>
         </is>
       </c>
     </row>
@@ -4194,68 +4194,63 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>He Yaqiong (何亚琼)</t>
+          <t>QS2027: 721-730</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 721-730</t>
+          <t>THE2027: 651-700</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 651-700</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 37</t>
         </is>
       </c>
-      <c r="V19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W19" s="4" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>• Tianxun-1 / TX-1 (2011, 60 kg microsat)
 • Zhizhou tethered satellite (2026, launched with Tianzhou-10)</t>
         </is>
       </c>
+      <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="4" t="inlineStr">
+      <c r="Y19" s="4" t="inlineStr">
         <is>
           <t>• College of Astronautics
 • College of Aerospace Engineering (incl. Intelligent Equipment Dynamics Center)</t>
         </is>
       </c>
-      <c r="AA19" s="4" t="inlineStr">
+      <c r="Z19" s="4" t="inlineStr">
         <is>
           <t>• Zhizhou flew on Tianzhou-10 cargo mission (China Manned Space programme)
 • IAF member since 2019</t>
         </is>
       </c>
-      <c r="AB19" s="4" t="inlineStr">
+      <c r="AA19" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC19" s="4" t="n">
+      <c r="AB19" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="AD19" s="5" t="inlineStr">
+      <c r="AC19" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="inlineStr"/>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
       <c r="AF19" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>• Новый секретарь парткома Хэ Яцюн с июня 2026
 • Сайт международного отдела (iao.nuaa.edu.cn) был недоступен — e-mail не подтверждён
@@ -4263,7 +4258,7 @@
 • Адресат: Официального e-mail отдела на сайте ico.nuaa.edu.cn не нашли, там есть только телефоны (общий: 025-84890911, начальник: 025-84891458, факс 025-84498069). Вопросы международных связей ведёт замначальника Чжан Гоцюань (张国权), а вопросы общего сектора — его руководитель Цзу Юйянь (祖语嫣). E-mail нужно уточнить по телефону</t>
         </is>
       </c>
-      <c r="AH19" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nuaa.edu.cn/481/list.htm
 • Https://news.sciencenet.cn/htmlnews/2026/6/566759.shtm
@@ -4281,9 +4276,14 @@
 • Http://ico.nuaa.edu.cn/10476/list.htm</t>
         </is>
       </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>He Yaqiong (何亚琼)</t>
         </is>
       </c>
     </row>
@@ -4381,43 +4381,38 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Jiang Hong (姜虹)</t>
+          <t>QS2027: 317</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 317</t>
+          <t>THE2027: =163</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =163</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 30</t>
         </is>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W20" s="4" t="inlineStr">
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>• Nanke-1 (南科一号 / Tianyi-34, SUSTech electric-field &amp; aurora-camera payloads, 2025)
 • Pengcheng Nanke-1 / PEGA-SUS 1 (鹏城南科一号, 5G NTN satellite with Peng Cheng Lab and GalaxySpace, SUSTech-led comms payload, 2026)</t>
         </is>
       </c>
+      <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="4" t="inlineStr">
+      <c r="Y20" s="4" t="inlineStr">
         <is>
           <t>• Department of Earth and Space Sciences (space physics
 • Electric-field and auroral instruments)
 • Department of Electronic and Electrical Engineering – Electromagnetic Information Lab</t>
         </is>
       </c>
-      <c r="AA20" s="4" t="inlineStr">
+      <c r="Z20" s="4" t="inlineStr">
         <is>
           <t>• Peng Cheng Laboratory
 • GalaxySpace
@@ -4426,26 +4421,26 @@
 • Guangzhou Chengxing Communications</t>
         </is>
       </c>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="n">
+      <c r="AA20" s="4" t="inlineStr"/>
+      <c r="AB20" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AD20" s="5" t="inlineStr">
+      <c r="AC20" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD20" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE20" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF20" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Платформы КА построены партнёрами (Tianyi, GalaxySpace/Peng Cheng Lab); вуз разработал полезные нагрузки
 • Один факультет в Unverified List (UVL) США — не Entity List
@@ -4454,7 +4449,7 @@
 • Адресат: global@sustech.edu.cn — «公共邮箱» департамента. Должность начальника (部长) на сайте не указана; Чэнь Хао значится как «部门负责人» (руководитель подразделения)</t>
         </is>
       </c>
-      <c r="AH20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sustech.edu.cn/zh/leadership.html
 • Https://news.eol.cn/dongtai/gxrs/202307/t20230701_2450265.shtml
@@ -4470,9 +4465,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Jiang Hong (姜虹)</t>
         </is>
       </c>
     </row>
@@ -4560,68 +4560,67 @@
           <t>President</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 243</t>
+        </is>
+      </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 243</t>
+          <t>THE2027: 234</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 234</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 14</t>
         </is>
       </c>
-      <c r="V21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W21" s="4" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>CAS-7B / BP-1 'Bei Ligong 1 hao' / BIT Progress-OSCAR 102 (2019, with CAMSAT)</t>
         </is>
       </c>
+      <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
-      <c r="Y21" s="4" t="inlineStr"/>
+      <c r="Y21" s="4" t="inlineStr">
+        <is>
+          <t>School of Aerospace Science and Technology (空天科学与技术学院)</t>
+        </is>
+      </c>
       <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>School of Aerospace Science and Technology (空天科学与技术学院)</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr">
         <is>
           <t>• CAMSAT (CAS-7B amateur satellite)
 • Participation in crewed spaceflight, BeiDou and Mars exploration programmes (per university profile)</t>
         </is>
       </c>
-      <c r="AB21" s="4" t="inlineStr">
+      <c r="AA21" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC21" s="4" t="n">
+      <c r="AB21" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AD21" s="5" t="inlineStr">
+      <c r="AC21" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE21" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF21" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>• Срок секретаря парткома Чжан Цзюня истёк в июле 2026; преемник на сайте не указан
 • Телефон: отдел международного сотрудничества; приёмная президента/парткома +86-10-68914247
@@ -4630,7 +4629,7 @@
 • Адресат: Общего e-mail отдела на сайте нет, найдены только личные адреса сотрудников. Начальник отдела — Чэнь Дуаньдуань (陈端端, 处长), см. https://international.bit.edu.cn/gywm/ksry/cld/index.htm. Её e-mail не опубликован. Можно адресовать письмо ей («Dear Director Chen,») и отправить через zongxin@. Данные поисковика о начальнике «Тан Шуйюань» устарели</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bit.edu.cn/gbxxgk/xxld_sjb/index.htm
 • Https://www.bit.edu.cn/gbxxgk/xxld_sjb/25b42cea6c414fdb9b2d05c0d04169fc.htm
@@ -4646,11 +4645,12 @@
 • Https://international.bit.edu.cn/gywm/ksry/jlhzs/index.htm</t>
         </is>
       </c>
-      <c r="AI21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
+      <c r="AI21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -4738,73 +4738,68 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Tan Tieniu (谭铁牛)</t>
+          <t>QS2027: 90</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 90</t>
+          <t>THE2027: 59</t>
         </is>
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 59</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 6</t>
         </is>
       </c>
-      <c r="V22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W22" s="4" t="inlineStr">
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>• Nanda-1 / Lobster-eye X-ray Detection Satellite (南大一号/龙虾眼X射线探测卫星, 2020-07-25). Also: science lead/participant in CHASE 'Xihe' solar satellite (2021-10-14)
 • NJU video remote-sensing payload launched on Kuaizhou-11 Y8 (2025-12-13)</t>
         </is>
       </c>
+      <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
-      <c r="Y22" s="4" t="inlineStr"/>
+      <c r="Y22" s="4" t="inlineStr">
+        <is>
+          <t>School of Astronomy and Space Science</t>
+        </is>
+      </c>
       <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>School of Astronomy and Space Science</t>
-        </is>
-      </c>
-      <c r="AA22" s="4" t="inlineStr">
         <is>
           <t>• Lobster-eye satellite with HKU Laboratory for Space Research, CAST (CASC 5th Academy) Institute 508 and SAST 805 subsidiary ASES
 • Xihe (CHASE) solar mission with CNSA</t>
         </is>
       </c>
-      <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="n">
+      <c r="AA22" s="4" t="inlineStr"/>
+      <c r="AB22" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AD22" s="5" t="inlineStr">
+      <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD22" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE22" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF22" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>• Сильный пользователь космических данных (рентгеновская астрономия, физика Солнца)
 • Опубликован только webmaster@nju.edu.cn; международный e-mail не подтверждён (по поиску stuex@nju.edu.cn)
 • Адресат: oice@nju.edu.cn — официальный ящик управления (подвал сайта wb.nju.edu.cn). Личный e-mail начальника alu@nju.edu.cn; по межвузовским проектам — Chen Nan (陈楠, chennan@nju.edu.cn, начальник офиса обменов и проектов)</t>
         </is>
       </c>
-      <c r="AH22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nju.edu.cn/ndgk/xrld.htm
 • Https://njunju.nju.edu.cn/EN/administrative_offices/list.htm
@@ -4817,9 +4812,14 @@
 • Https://wb.nju.edu.cn/jgsz/list.htm</t>
         </is>
       </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Tan Tieniu (谭铁牛)</t>
         </is>
       </c>
     </row>
@@ -4918,36 +4918,31 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>Li Zhongjun (李忠军)</t>
+          <t>QS2027: 309</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 309</t>
+          <t>THE2027: =263</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =263</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 22</t>
         </is>
       </c>
-      <c r="V23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W23" s="4" t="inlineStr">
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>• Weiming-1 / Mofulong (未名一号/默孚龙号, ~30 kg, co-developed by PKU, SDU and MinoSpace
 • SDU built neutron spectrometer and Langmuir probe payloads) (Jan 2024)</t>
         </is>
       </c>
+      <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="4" t="inlineStr"/>
-      <c r="Z23" s="4" t="inlineStr">
+      <c r="Y23" s="4" t="inlineStr">
         <is>
           <t>• Institute of Space Sciences / School of Space Science and Physics (空间科学研究院 / 空间科学与物理学院, Weihai)
 • Space Science Climbing Team
@@ -4955,32 +4950,32 @@
 • School of Mechanical, Electrical and Information Engineering (Weihai)</t>
         </is>
       </c>
-      <c r="AA23" s="4" t="inlineStr">
+      <c r="Z23" s="4" t="inlineStr">
         <is>
           <t>• Peking University and MinoSpace (Weiming-1 joint satellite)
 • Listed in China University Planetary Science Alliance navbox (Wikipedia)</t>
         </is>
       </c>
-      <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="n">
+      <c r="AA23" s="4" t="inlineStr"/>
+      <c r="AB23" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AD23" s="5" t="inlineStr">
+      <c r="AC23" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE23" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF23" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• 1 КА: Weiming-1 совместно с PKU и MinoSpace; вклад вуза — 2 полезные нагрузки
 • Космический центр — кампус Вэйхай (fxipo@wh.sdu.edu.cn, +86-631-5688016)
@@ -4988,7 +4983,7 @@
 • Адресат: Личный e-mail: mawen@sdu.edu.cn. Сотрудничество с Россией и ШОС курирует зам. руководителя Zhou Chuan'en (周传恩), czhou@sdu.edu.cn; международные обмены в целом — Zhang Jiaqi (张佳琦), jqzhang@sdu.edu.cn</t>
         </is>
       </c>
-      <c r="AH23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sdu.edu.cn/sdgk/xrld.htm
 • Https://www.en.sdu.edu.cn/Contact_Us.htm
@@ -5000,9 +4995,14 @@
 • Https://www.ipo.sdu.edu.cn/bmjk/ryfg.htm</t>
         </is>
       </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Li Zhongjun (李忠军)</t>
         </is>
       </c>
     </row>
@@ -5092,70 +5092,65 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Cao Ping (曹萍)</t>
+          <t>QS2027: 488</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 488</t>
+          <t>THE2027: 351–375</t>
         </is>
       </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 351–375</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 33</t>
         </is>
       </c>
-      <c r="V24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W24" s="4" t="inlineStr">
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>UESTC-sat / 'Dianzi Keji Daxue hao' (电子科技大学号, Xingshidai-12 / Tianyan-05, 6G terahertz test satellite co-developed with ADASpace, 2020)</t>
         </is>
       </c>
+      <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="4" t="inlineStr"/>
+      <c r="Y24" s="4" t="inlineStr">
+        <is>
+          <t>School of Aeronautics and Astronautics (Institute of Aerospace Science and Technology): Navigation, Guidance &amp; TT&amp;C Research Center, Optical Communication Research Center, space microwave and space laser communication groups</t>
+        </is>
+      </c>
       <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>School of Aeronautics and Astronautics (Institute of Aerospace Science and Technology): Navigation, Guidance &amp; TT&amp;C Research Center, Optical Communication Research Center, space microwave and space laser communication groups</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="inlineStr">
         <is>
           <t>• ADASpace (Guoxing Aerospace) – 6G test satellite
 • Huantian Smart Technology (naming of Chengdian-1, 2026)
 • Applications in China's crewed spaceflight programme (per school profile)</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr">
+      <c r="AA24" s="4" t="inlineStr">
         <is>
           <t>Entity List США</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="n">
+      <c r="AB24" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AD24" s="5" t="inlineStr">
+      <c r="AC24" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE24" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF24" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• В Entity List США (с 2012)
 • Chengdian-1 (март 2026) носит имя вуза, но построен компанией Huantian — не учтён
@@ -5164,7 +5159,7 @@
 • Адресат: zhaoban@uestc.edu.cn — ящик приёмной комиссии (招生办), для партнёрского письма не подходит. international@uestc.edu.cn взят из выдачи поиска по en.uestc.edu.cn/index/Contact_Us.htm, но саму страницу открыть не удалось (JS-защита) — проверить. Сайт отдела oice.uestc.edu.cn закрыт антиботом; имя начальника не подтверждено (в поиске встречаются разные имена: 高世全, 邸爱英)</t>
         </is>
       </c>
-      <c r="AH24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uestc.edu.cn/xxgk/xrld.htm
 • Http://www.xinhuanet.com/edu/20240223/1119ae399c4d48ecb0f7932a54fe9182/c.html
@@ -5181,9 +5176,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Cao Ping (曹萍)</t>
         </is>
       </c>
     </row>
@@ -5277,11 +5277,10 @@
       <c r="R25" s="4" t="inlineStr"/>
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="W25" s="4" t="inlineStr">
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>• Tiantuo-1 (2012)
 • Tiantuo-2 (2014, video microsat)
@@ -5290,42 +5289,42 @@
 • Tiantuo-5 (2020, 78.5 kg)</t>
         </is>
       </c>
+      <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="4" t="inlineStr"/>
+      <c r="Y25" s="4" t="inlineStr">
+        <is>
+          <t>College of Aerospace Science and Engineering (空天科学学院)</t>
+        </is>
+      </c>
       <c r="Z25" s="4" t="inlineStr">
         <is>
-          <t>College of Aerospace Science and Engineering (空天科学学院)</t>
+          <t>QB50 (NUDTSat)</t>
         </is>
       </c>
       <c r="AA25" s="4" t="inlineStr">
         <is>
-          <t>QB50 (NUDTSat)</t>
-        </is>
-      </c>
-      <c r="AB25" s="4" t="inlineStr">
-        <is>
           <t>Entity List США</t>
         </is>
       </c>
-      <c r="AC25" s="4" t="n">
+      <c r="AB25" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AD25" s="5" t="inlineStr">
+      <c r="AC25" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD25" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE25" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF25" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>• Военный вуз НОАК — не входит в рейтинги QS/THE/BCUR; участие в гражданской группировке маловероятно
 • Вместо секретаря парткома — политкомиссар; имя не подтверждено
@@ -5335,7 +5334,7 @@
 • Адресат: Военный вуз (НОАК), состав руководства отдела иностранных дел не публикуется. Адрес fao@nudt.edu.cn подтверждён в контактах англоязычного сайта (тел. +86-731-87000275). Имя руководителя установить нельзя. Учтите, что университет включён в санкционные списки США (Entity List)</t>
         </is>
       </c>
-      <c r="AH25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>• Https://news.eol.cn/dongtai/gxrs/202606/t20260629_2750325.shtml
 • Https://english.nudt.edu.cn/
@@ -5349,11 +5348,12 @@
 • Nanosats.eu export (local nanosats.csv)</t>
         </is>
       </c>
-      <c r="AI25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
+      <c r="AI25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -5426,62 +5426,57 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Lu Guibin (路贵斌)</t>
+          <t>QS2027: 675</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 675</t>
+          <t>THE2027: 551-600</t>
         </is>
       </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 551-600</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 36</t>
         </is>
       </c>
-      <c r="V26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W26" s="4" t="inlineStr">
+      <c r="V26" s="4" t="inlineStr">
         <is>
           <t>• NJUST-1, QB50 BE03 (2017)
 • Tianyuan-1, 6U (2021)</t>
         </is>
       </c>
+      <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
-      <c r="Z26" s="4" t="inlineStr"/>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
+          <t>QB50 (NJUST-1)</t>
+        </is>
+      </c>
       <c r="AA26" s="4" t="inlineStr">
-        <is>
-          <t>QB50 (NJUST-1)</t>
-        </is>
-      </c>
-      <c r="AB26" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC26" s="4" t="n">
+      <c r="AB26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD26" s="5" t="inlineStr">
+      <c r="AC26" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AE26" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
       <c r="AF26" s="4" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>• Сайт njust.edu.cn закрыт антибот-защитой — страницы руководства и контактов не открылись
 • Руководство взято из китайской Википедии, не подтверждено на 2025–2026 — перепроверить
@@ -5489,7 +5484,7 @@
 • Адресат: Сайты njust.edu.cn (включая gjc.njust.edu.cn и english.njust.edu.cn) закрыты анти-бот защитой (JS-челлендж), страницы прочитать не удалось. Ни e-mail отдела, ни имя начальника подтвердить нельзя, нужно проверить вручную в браузере</t>
         </is>
       </c>
-      <c r="AH26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Nanjing_University_of_Science_and_Technology
 • Https://zh.wikipedia.org/zh-cn/南京理工大学
@@ -5503,9 +5498,14 @@
 • Https://gjc.njust.edu.cn/</t>
         </is>
       </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Lu Guibin (路贵斌)</t>
         </is>
       </c>
     </row>
@@ -5599,35 +5599,30 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>Tian Hui (田辉)</t>
+          <t>QS2027: 488</t>
         </is>
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 488</t>
+          <t>THE2027: 376-400</t>
         </is>
       </c>
       <c r="T27" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 376-400</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 26</t>
         </is>
       </c>
-      <c r="V27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W27" s="4" t="inlineStr">
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>Jilin University-1 / Jitianxing A-01 (吉林大学一号/吉天星A-01星, metre-class push-broom optical remote-sensing satellite, Jielong-3, 24 Sep 2024)</t>
         </is>
       </c>
+      <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="4" t="inlineStr"/>
-      <c r="Z27" s="4" t="inlineStr">
+      <c r="Y27" s="4" t="inlineStr">
         <is>
           <t>• College of Instrumentation and Electrical Engineering (仪器科学与电气工程学院, led the satellite
 • Zhang Liu team under Academician Lin Jun)
@@ -5635,27 +5630,27 @@
 • College of Geo-Exploration Science and Technology</t>
         </is>
       </c>
+      <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="n">
+      <c r="AB27" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AD27" s="5" t="inlineStr">
+      <c r="AC27" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE27" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF27" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• Новый секретарь парткома Тянь Хуэй (ранее Цзян Чжиин)
 • КА Jilin University-1 (2024): первый снимок через 38 ч после запуска; второй КА не подтверждён
@@ -5664,7 +5659,7 @@
 • Адресат: Служебный ящик директора: director_global@jlu.edu.cn (можно поставить в копию). Сотрудничество/платформы курирует зам. начальника Gao Yixing (高一星), gaoyixing@jlu.edu.cn</t>
         </is>
       </c>
-      <c r="AH27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• Https://www.jlu.edu.cn/xxgk/xrld.htm
 • Https://oic.jlu.edu.cn/
@@ -5679,9 +5674,14 @@
 • Http://oic.jlu.edu.cn/gywm/bmld.htm</t>
         </is>
       </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Tian Hui (田辉)</t>
         </is>
       </c>
     </row>
@@ -5773,57 +5773,52 @@
           <t>President</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr">
-        <is>
-          <t>Li Ruxin (李儒新)</t>
-        </is>
-      </c>
+      <c r="R28" s="4" t="inlineStr"/>
       <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="inlineStr">
+      <c r="T28" s="4" t="inlineStr">
         <is>
           <t>BCUR2026: 47</t>
         </is>
       </c>
-      <c r="V28" s="4" t="n">
+      <c r="U28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W28" s="4" t="inlineStr">
+      <c r="V28" s="4" t="inlineStr">
         <is>
           <t>• STU-2A/2B/2C (上科大二号, three CubeSats aka TW-1A/B/C, 2015-09-25, Long March 11
 • Developed by Shanghai Engineering Centre for Microsatellites with ShanghaiTech). STU-1 (QB50) was cancelled</t>
         </is>
       </c>
+      <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
-      <c r="Z28" s="4" t="inlineStr"/>
-      <c r="AA28" s="4" t="inlineStr">
+      <c r="Z28" s="4" t="inlineStr">
         <is>
           <t>• Co-founded by Shanghai Municipal Government and Chinese Academy of Sciences
 • Science-education partnership with Shanghai Engineering Centre for Microsatellites / CAS Innovation Academy for Microsatellites (SECM/IAMCAS)
 • Former QB50 participant (STU-1, cancelled)</t>
         </is>
       </c>
-      <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="n">
+      <c r="AA28" s="4" t="inlineStr"/>
+      <c r="AB28" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AD28" s="5" t="inlineStr">
+      <c r="AC28" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD28" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE28" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF28" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>• КА STU-2 носят имя вуза, но построены SECM (CAS); роль вуза — научное и образовательное использование
 • Связь с CAS — выход на экспертизу IAMCAS по микроспутникам
@@ -5831,7 +5826,7 @@
 • Адресат: Должности начальника нет — управлением руководит зам. начальника Nie Yan (nieyan@shanghaitech.edu.cn). Международными программами занимается Xiao Yin (肖茵, помощник начальника, xiaoyin@shanghaitech.edu.cn) — можно в копию</t>
         </is>
       </c>
-      <c r="AH28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>• Https://www.shanghaitech.edu.cn/2025/1223/c1584a1118320/page.htm
 • Http://www.shanghaitech.edu.cn/en/1059/list.htm
@@ -5843,9 +5838,14 @@
 • Https://oia.shanghaitech.edu.cn/549/list.htm</t>
         </is>
       </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Li Ruxin (李儒新)</t>
         </is>
       </c>
     </row>
@@ -5881,24 +5881,24 @@
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="45" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="55" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="24" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5989,92 +5989,92 @@
       </c>
       <c r="R1" s="3" t="inlineStr">
         <is>
-          <t>Секретарь парткома</t>
+          <t>Рейтинг QS</t>
         </is>
       </c>
       <c r="S1" s="3" t="inlineStr">
         <is>
-          <t>Рейтинг QS</t>
+          <t>Рейтинг THE</t>
         </is>
       </c>
       <c r="T1" s="3" t="inlineStr">
         <is>
-          <t>Рейтинг THE</t>
+          <t>Национальный рейтинг</t>
         </is>
       </c>
       <c r="U1" s="3" t="inlineStr">
         <is>
-          <t>Национальный рейтинг</t>
+          <t>Запущено КА (спутников)</t>
         </is>
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
-          <t>Запущено КА (спутников)</t>
+          <t>Названия запущенных КА (год)</t>
         </is>
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>Названия запущенных КА (год)</t>
+          <t>КА в разработке</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
         <is>
-          <t>КА в разработке</t>
+          <t>Наземная станция</t>
         </is>
       </c>
       <c r="Y1" s="3" t="inlineStr">
         <is>
-          <t>Наземная станция</t>
+          <t>Космические подразделения</t>
         </is>
       </c>
       <c r="Z1" s="3" t="inlineStr">
         <is>
-          <t>Космические подразделения</t>
+          <t>Партнёрства в космической сфере</t>
         </is>
       </c>
       <c r="AA1" s="3" t="inlineStr">
         <is>
-          <t>Партнёрства в космической сфере</t>
+          <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
       <c r="AB1" s="3" t="inlineStr">
         <is>
-          <t>Санкционные / ограничительные списки (США)</t>
+          <t>Космический индекс (0–100)</t>
         </is>
       </c>
       <c r="AC1" s="3" t="inlineStr">
         <is>
-          <t>Космический индекс (0–100)</t>
+          <t>Волна рассылки</t>
         </is>
       </c>
       <c r="AD1" s="3" t="inlineStr">
         <is>
-          <t>Волна рассылки</t>
+          <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
       <c r="AE1" s="3" t="inlineStr">
         <is>
-          <t>Проверка домена e-mail (MX)</t>
+          <t>Достоверность</t>
         </is>
       </c>
       <c r="AF1" s="3" t="inlineStr">
         <is>
-          <t>Достоверность</t>
+          <t>Примечания</t>
         </is>
       </c>
       <c r="AG1" s="3" t="inlineStr">
         <is>
-          <t>Примечания</t>
+          <t>Источники</t>
         </is>
       </c>
       <c r="AH1" s="3" t="inlineStr">
         <is>
-          <t>Источники</t>
+          <t>Дата проверки</t>
         </is>
       </c>
       <c r="AI1" s="3" t="inlineStr">
         <is>
-          <t>Дата проверки</t>
+          <t>Секретарь парткома (справочно, Китай)</t>
         </is>
       </c>
     </row>
@@ -6167,79 +6167,74 @@
       </c>
       <c r="R2" s="4" t="inlineStr">
         <is>
-          <t>Qiu Xin (裘新)</t>
+          <t>QS2027: 26</t>
         </is>
       </c>
       <c r="S2" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 26</t>
+          <t>THE2027: 38</t>
         </is>
       </c>
       <c r="T2" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 38</t>
-        </is>
-      </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 5</t>
         </is>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>• Fudan Information Star / Jiguang constellation-01 (复旦信息星, 2024-05-31, Ceres-1)
 • Fudan-1 / Lancang-Mekong Future Star (复旦一号/澜湄未来星, ~50 kg, 2024-09)
 • Fuyao (复遥号, 2024-11-11)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>• School of Information Science &amp; Engineering says its next technology test satellite is in preparation (2024)
 • No name published</t>
         </is>
       </c>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>Fudan University satellite ground station (复旦大学卫星地面站) receives real-time Fuyao data; bands not published</t>
+        </is>
+      </c>
       <c r="Y2" s="4" t="inlineStr">
-        <is>
-          <t>Fudan University satellite ground station (复旦大学卫星地面站) receives real-time Fuyao data; bands not published</t>
-        </is>
-      </c>
-      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>• School of Information Science and Engineering (Jin Yaqiu group, space-borne remote sensing/laser comms)
 • Department of Nuclear Science and Technology (Fudan-1 solar UV spectrometer)
 • Lancang-Mekong Youth Astronomical Science Research Centre (2025)</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>• Fudan-1 co-developed with Shanghai Academy of Spaceflight Technology (CASC 8th Academy) / Shanghai Aerospace Space Technology Co
 • Fudan-1 data shared with the six Lancang-Mekong (LMC) countries
 • Jiguang constellation with HiStarlink (laser communications) and Shanghai Dianji University</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="AB2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AC2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD2" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE2" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF2" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• 3 КА в 2024, собственная наземная станция, опыт международного проекта Ланьцан–Меконг — сильный партнёр
 • Fudan-1 и Fuyao созданы совместно с промышленностью (SAST)
@@ -6247,7 +6242,7 @@
 • Адресат: ogp@fudan.edu.cn указан на странице контактов как ящик «综合业务» (общая работа отдела). Личный e-mail начальника: lalu@fudan.edu.cn — можно поставить в копию</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fudan.edu.cn/448/list.htm
 • Https://www.fudan.edu.cn/en/Contact_931/list.htm
@@ -6262,9 +6257,14 @@
 • Https://ogp.fudan.edu.cn/16079/list.htm</t>
         </is>
       </c>
+      <c r="AH2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Qiu Xin (裘新)</t>
         </is>
       </c>
     </row>
@@ -6362,28 +6362,23 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>Zhang Yunming (张云明)</t>
+          <t>QS2027: 425</t>
         </is>
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 425</t>
+          <t>THE2027: =224</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =224</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 23</t>
         </is>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>• Aoxiang Zhixing / Star of Aoxiang, first 12U CubeSat (2016)
 • Xingyun Shiyan-1 / XY-S1 (2017)
@@ -6393,51 +6388,51 @@
 • Qinling-01 &amp; Qinling-02 (2026, 150 kg sub-metre imaging)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>Qinling Constellation planned at 36 satellites (visible, hyperspectral, SAR) for Shaanxi province</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>• School of Astronautics
 • School of Aeronautics
 • Micro-satellite team (Aoxiang series)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• Macau Science-1 with Macau University of Science and Technology and CAST DFH Satellite Co
 • QB50 (Aoxiang-1)
 • IAF member since 2019</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE3" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF3" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Новый секретарь парткома Чжан Юньмин (экс-замминистра MIIT) с мая 2026
 • Телефон и e-mail: отдел международного сотрудничества (г-жа Чэн Инь); альтернативно fao@nwpu.edu.cn, +86-29-88492267
@@ -6445,7 +6440,7 @@
 • Адресат: wgzj@nwpu.edu.cn (wgzj = «иностранные специалисты») — адрес сектора иностранных специалистов, контактное лицо г-жа Чэн Инь (Cheng Yin, тел. 88492812): https://en.nwpu.edu.cn/EnglishNew/index/contactus.htm. Сейчас официальный адрес отдела — nwpuge@nwpu.edu.cn. Сайт защищён от ботов, страница прочитана через WebFetch (пересказ). Замначальника отдела — Ли Цзывэй (李自伟) и Чэнь Цзюнь (陈俊)</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.acabridge.cn/yxxw/gxrs/202605/t20260509_2733421.shtml
 • Https://en.nwpu.edu.cn/EnglishNew/index/contactus.htm
@@ -6462,9 +6457,14 @@
 • Https://guoji.nwpu.edu.cn/jggk/lxwm.htm</t>
         </is>
       </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Zhang Yunming (张云明)</t>
         </is>
       </c>
     </row>
@@ -6562,46 +6562,41 @@
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>Liu Chenggong (刘承功)</t>
+          <t>QS2027: 258</t>
         </is>
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 258</t>
+          <t>THE2027: =205</t>
         </is>
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =205</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 13</t>
         </is>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>• TianQin-1 (天琴一号, technology test satellite co-developed with HUST and DFH Satellite Co., 2019)
 • Yixian-A (逸仙-A, student 3U CubeSat with wooden panels, 2025
 • First attempt lost in a 2024 launch failure)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>• TianQin programme: Step 2 dual-satellite laser-interferometry test (in progress)
 • Step 3 three-satellite TianQin gravitational-wave observatory (~100,000 km orbit, target ~2035)</t>
         </is>
       </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>TianQin Center operates a lunar/satellite laser ranging station (Zhuhai) and ground stations for satellite data collection (bands not published)</t>
+        </is>
+      </c>
       <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>TianQin Center operates a lunar/satellite laser ranging station (Zhuhai) and ground stations for satellite data collection (bands not published)</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics (Shenzhen campus)
 • TianQin Research Center for Gravitational Physics (MOE Key Lab
@@ -6611,7 +6606,7 @@
 • School of Atmospheric Sciences</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>• CNSA (TianQin-1 accepted by CNSA, rated 'excellent'
 • TianQin Center hosts a CNSA research centre)
@@ -6619,26 +6614,26 @@
 • HUST</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
+      <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE4" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF4" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Смена руководства: секретарь парткома Лю Чэнгун (ноябрь 2025), президент Тан Хунъу (июль 2026); собственная страница вуза устарела
 • Входит в Unverified List (UVL) Минторга США — не Entity List
@@ -6647,7 +6642,7 @@
 • Адресат исправлен: с июля 2026 президент — Тан Хунъу (Гао Сун перешёл в PKU)</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.news.cn/politics/20260703/0805d89b4e584a0682a9ed20f1a5291f/c.html
 • Https://edu.cnr.cn/dj/20251120/t20251120_527435649.shtml
@@ -6665,9 +6660,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Liu Chenggong (刘承功)</t>
         </is>
       </c>
     </row>
@@ -6761,46 +6761,41 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>Shu Gequn (舒歌群)</t>
+          <t>QS2027: 134</t>
         </is>
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 134</t>
+          <t>THE2027: =51</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =51</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 7</t>
         </is>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>• Micius / QUESS (墨子号, world's first quantum science satellite, USTC-led, 2016)
 • Jinan-1 (济南一号, quantum micro-nano satellite, led by Hefei National Laboratory with USTC and Jinan Institute of Quantum Technology, 2022)</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>• MERLIS 12U CubeSat (mm-wave satcom/UHD video
 • Listed as not launched on nanosats.eu)
 • Planned quantum micro-nano satellite constellation</t>
         </is>
       </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>Portable/mobile quantum optical ground stations (&lt;100 kg) used with Jinan-1 for real-time satellite-to-ground QKD (incl. link to Stellenbosch, South Africa)</t>
+        </is>
+      </c>
       <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>Portable/mobile quantum optical ground stations (&lt;100 kg) used with Jinan-1 for real-time satellite-to-ground QKD (incl. link to Stellenbosch, South Africa)</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>• School of Earth and Space Sciences
 • CAS Key Laboratory of Quantum Information
@@ -6808,7 +6803,7 @@
 • Department of Modern Physics / Deep space &amp; astrophysics groups</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>• Chinese Academy of Sciences (USTC is a CAS university
 • Micius was a CAS Strategic Priority project)
@@ -6818,26 +6813,26 @@
 • Stellenbosch University (South Africa, BRICS quantum link)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD5" s="5" t="inlineStr">
+      <c r="AC5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE5" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF5" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• В Entity List США входит лаборатория при USTC (Hefei National Laboratory), сам вуз — нет
 • Президент Чан Цзинь с октября 2024; Пань Цзяньвэй руководит квантовыми спутниками
@@ -6846,7 +6841,7 @@
 • Адресат: oic@ustc.edu.cn указан на oic.ustc.edu.cn; в шапке сайта как «通联邮箱» указан также fanjiangqi@ustc.edu.cn. Личный адрес начальника: qukun@ustc.edu.cn</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ustc.edu.cn/xxgk/xrld.htm
 • Https://news.ustc.edu.cn/info/1055/89173.htm
@@ -6864,9 +6859,14 @@
 • Https://oic.ustc.edu.cn/%e5%85%b3%e4%ba%8e%e6%88%91%e4%bb%ac/%e4%ba%ba%e5%91%98%e4%bf%a1%e6%81%af/</t>
         </is>
       </c>
+      <c r="AH5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Shu Gequn (舒歌群)</t>
         </is>
       </c>
     </row>
@@ -6957,28 +6957,23 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>Zhu Kongjun (朱孔军)</t>
+          <t>QS2027: 165</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 165</t>
+          <t>THE2027: =121</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =121</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 8</t>
         </is>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="U6" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>• Luojia-1 01 (珞珈一号01星, night-light 6U, 2018)
 • Qimingxing-1 (启明星一号, student microsat, 2022)
@@ -6988,18 +6983,18 @@
 • Luojia-4 01 'People's Health' (珞珈四号01星, medical remote sensing, 2024)</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>• Dongfang Huiyan (Oriental SmartEye) intelligent remote-sensing constellation with Yantai municipality (phased to 200+ satellites by 2030
 • First high-res satellite launched Feb 2024, WHU as chief scientist/designer)</t>
         </is>
       </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>Wuhan University Remote Sensing Satellite Ground Station (operational Dec 2012; 13 m X/S dual-band and 12 m Ka/X/S tri-band TT&amp;C/data-receiving systems; master station for all Luojia satellites; supported Chang'e-3/5 and Tianwen-1 tracking)</t>
+        </is>
+      </c>
       <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>Wuhan University Remote Sensing Satellite Ground Station (operational Dec 2012; 13 m X/S dual-band and 12 m Ka/X/S tri-band TT&amp;C/data-receiving systems; master station for all Luojia satellites; supported Chang'e-3/5 and Tianwen-1 tracking)</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>• State Key Laboratory of Information Engineering in Surveying, Mapping and Remote Sensing (LIESMARS)
 • School of Remote Sensing and Information Engineering
@@ -7008,7 +7003,7 @@
 • GNSS Research Center</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>• CAST / DFH Satellite Co. (Luojia-3 01 co-design)
 • CASIC (Kuaizhou launches)
@@ -7016,26 +7011,26 @@
 • Support to CNSA lunar/Mars missions via ground station</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD6" s="5" t="inlineStr">
+      <c r="AC6" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE6" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF6" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Сильнейший в выборке оператор спутников и ДЗЗ, собственная наземная станция Ka/X/S — приоритетный партнёр
 • Секретарь парткома Чжу Кунцзюнь с сентября 2025
@@ -7045,7 +7040,7 @@
 • Адресат: Адрес fao@whu.edu.cn взят с en.whu.edu.cn/Contact_Us/Office_of_International_Affairs.htm (Section of General Affairs). Страница руководства обновлена 2026-09-09; Дэн Хэсян руководит всей работой и курирует общий отдел</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Https://www.whu.edu.cn/xxgk/xrld.htm
 • Https://www.news.cn/politics/20250919/f203a39343a1422fbe1dcfbda5f74872/c.html
@@ -7067,9 +7062,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Zhu Kongjun (朱孔军)</t>
         </is>
       </c>
     </row>
@@ -7144,24 +7144,19 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>Xu Mei (续梅)</t>
-        </is>
-      </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
           <t>QS2027: 1001-1200</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>BCUR2026: 50</t>
         </is>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>• BUPT-Galaxy (北邮-银河号, with GalaxySpace, 2022)
 • BUPT-1 (北邮一号, 12U, Tiansuan constellation main satellite, 2023)
@@ -7170,24 +7165,24 @@
 • BUPT-4 (北邮四号, 50 kg class, with Tianyi/Spacety, 2026)</t>
         </is>
       </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>Tiansuan (天算) space-computing constellation phase 2 (reported plan of ~24 satellites)</t>
+        </is>
+      </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>Tiansuan (天算) space-computing constellation phase 2 (reported plan of ~24 satellites)</t>
+          <t>Tiansuan constellation ground segment incl. an East China (Shandong) ground station and a 'space computing cloud' ground-station service platform (bands not published)</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>Tiansuan constellation ground segment incl. an East China (Shandong) ground station and a 'space computing cloud' ground-station service platform (bands not published)</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>• Tiansuan Constellation programme (Prof. Wang Shangguang team, State Key Lab of Networking and Switching Technology)
 • BUPT Shenzhen Research Institute
 • Space computing / satellite internet research groups</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>• Changsha Tianyi Research Institute (Spacety)
 • GalaxySpace
@@ -7198,26 +7193,26 @@
 • Yantai University</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Entity List США</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AB7" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="inlineStr"/>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
       <c r="AF7" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Сайты вуза блокировали запросы — контакты не подтверждены; по поиску: межд. отдел +86-10-62281949, admissions@bupt.edu.cn
 • В Entity List США
@@ -7226,7 +7221,7 @@
 • Адресат: Все сайты BUPT (www, io.bupt.edu.cn, english) отдают 412 (антибот-защита), страницы открыть не удалось. По результатам поиска начальником может быть Чэнь Янь (陈岩), но это не подтверждено открытой страницей. Официальный адрес отдела для партнёрств не найден (найдены только адреса приёма иностранных студентов)</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Https://news.qq.com/rain/a/20260920V0D5QV00
 • Https://peking.bjd.com.cn/content/s6ab274fde4b0e42f8f00ab63.html
@@ -7243,9 +7238,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Xu Mei (续梅)</t>
         </is>
       </c>
     </row>
@@ -7343,73 +7343,68 @@
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>Cheng Jianping (程建平)</t>
+          <t>QS2027: 237</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 237</t>
+          <t>THE2027: 125</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 125</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 19</t>
         </is>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="U8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>• BNU-1 / Jingshi-1 polar-observation smallsat (京师一号, ~16 kg, 2019-09-12
 • Built for BNU by Shenzhen Aerospace Dongfanghong HIT Satellite)
 • MuDuo-1A and MuDuo-1B instant remote-sensing constellation (木铎一号, 2026-08-25)</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Further expansion of the MuDuo (木铎) satellite network constellation</t>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Geographical Science
 • Institute of Global Change and Earth System Science
 • Frontier Interdisciplinary Research Institute for Satellite Applications (卫星应用前沿交叉研究院)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>• BNU-1 co-funded by Ministry of Science and Technology
 • Built by Shenzhen Aerospace Dongfanghong HIT Satellite Ltd (CAST/HIT)</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
+      <c r="AC8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE8" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF8" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Пользователь и оператор спутников ДЗЗ: BNU-1 (полярные наблюдения) и группировка MuDuo (2026)
 • Общий e-mail — адрес новостного центра
@@ -7417,7 +7412,7 @@
 • Адресат: Исходный oiec3@bnu.edu.cn принадлежит Fang Shunji (方顺姬) — сотруднику по студенческим выездным обменам (Азия, Африка); для приглашения к институциональному партнёрству не подходит. Liu Min отвечает за межвузовские обмены и проекты сотрудничества. Начальник отдела — Teng Jun (滕珺, tengjun1983@bnu.edu.cn) — рекомендуется в копию</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bnu.edu.cn/xxgk/xrld/index.htm
 • Https://english.bnu.edu.cn/dblj1/contactus/index.htm
@@ -7430,9 +7425,14 @@
 • Https://oiec.bnu.edu.cn/gywm/lxwm/index.htm</t>
         </is>
       </c>
+      <c r="AH8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Cheng Jianping (程建平)</t>
         </is>
       </c>
     </row>
@@ -7526,28 +7526,23 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>Ren Shaobo (任少波)</t>
+          <t>QS2027: 47</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 47</t>
+          <t>THE2027: 34</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 34</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 3</t>
         </is>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>• ZDPS-1 / Pixing-1 MEMS-Pico (2007, no signal)
 • ZDPS-1A x2 / Pixing-1A (2010)
@@ -7557,44 +7552,44 @@
 • WJ-1B, Oman's first satellite (2024)</t>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <t>In Aug 2020 ZJU said it planned ~20 more satellites within a year (status not verified)</t>
         </is>
       </c>
-      <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr"/>
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics
 • Micro-Satellite Research Center (School of Information and Electronic Engineering)
 • Spacecraft intelligent technology team</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr">
         <is>
           <t>WJ-1B built for Oman (Oman's first satellite), assembly/test support from CAST 5th Academy</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AD9" s="5" t="inlineStr">
+      <c r="AC9" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE9" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF9" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Телефон/e-mail: Office of Global Engagement (кампус Цзыцзиньган)
 • 8 КА — по перечисленным запускам; вероятно больше, требуется проверка
@@ -7602,7 +7597,7 @@
 • Адресат: Личный адрес начальника — jyleung@zju.edu.cn. В Офисе по сотрудничеству (合作交流办公室) Африку и Латинскую Америку курирует Сунь Мо (孙墨, mosun@zju.edu.cn), Россию — Ху Линьюань (胡临远, jo.huly@zju.edu.cn), Азию — Чжан Чуюнь (张楚韵, zhangchuyun@zju.edu.cn). Их стоит поставить в копию</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Https://www.zju.edu.cn/xrld/list.htm
 • Https://www.zju.edu.cn/2025/0328/c76679a3032574/page.htm
@@ -7618,9 +7613,14 @@
 • Http://www.ir.zju.edu.cn/69632/list.htm</t>
         </is>
       </c>
+      <c r="AH9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Ren Shaobo (任少波)</t>
         </is>
       </c>
     </row>
@@ -7714,73 +7714,68 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>Yang Zhenbin (杨振斌)</t>
+          <t>QS2027: 36</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 36</t>
+          <t>THE2027: 39</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 39</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 4</t>
         </is>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>• APSCO-SSS-2A / SJTU Siyuan-1 (思源一号, 3U, 2021)
 • ICUBE-Q / SJTU Siyuan-2 (思源二号, lunar-orbit CubeSat co-developed with Pakistan's IST, carried by Chang'e-6, 2024)</t>
         </is>
       </c>
-      <c r="X10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>Ground ops capability at Intelligent Satellite Technology Center (team ran first-signal monitoring for SSS-2A at a Kashgar test station); no dedicated university station with bands verified</t>
+        </is>
+      </c>
       <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>Ground ops capability at Intelligent Satellite Technology Center (team ran first-signal monitoring for SSS-2A at a Kashgar test station); no dedicated university station with bands verified</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics
 • Intelligent Satellite Technology Center (SSTC, led by IAA academician Wu Shufan)
 • SJTU–Shanghai Institute of Satellite Engineering joint graduate training base</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>• APSCO (Student Small Satellite project SSS-2A)
 • CNSA Chang'e-6 international payload (ICUBE-Q with Pakistan IST/SUPARCO side)
 • Shanghai Institute of Satellite Engineering (CASC/SAST) joint training base</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="n">
+      <c r="AA10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AD10" s="5" t="inlineStr">
+      <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD10" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE10" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF10" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Команда также участвовала в STU-2 (3 кубсата, 2015) и SDS-1, но они велись другими организациями — не учтены
 • Общий e-mail не опубликован; использовать международный отдел globalsjtu@sjtu.edu.cn
@@ -7788,7 +7783,7 @@
 • Адресат: globalsjtu@sjtu.edu.cn указан как общий ящик отдела на global.sjtu.edu.cn/about/contact; личный адрес начальника: htyin@sjtu.edu.cn</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Https://dzb.sjtu.edu.cn/Data/List/xzjs
 • Https://news.qq.com/rain/a/20260914A0DOCS00
@@ -7806,9 +7801,14 @@
 • Https://global.sjtu.edu.cn/about/organization</t>
         </is>
       </c>
+      <c r="AH10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Yang Zhenbin (杨振斌)</t>
         </is>
       </c>
     </row>
@@ -7902,42 +7902,37 @@
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>Liu Jie (刘杰)</t>
+          <t>QS2027: =677</t>
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>QS2027: =677</t>
+          <t>THE2022: 801-1000 (not listed in later editions)</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>THE2022: 801-1000 (not listed in later editions)</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 56</t>
         </is>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>• Dizhi-1 / Geology-1 (地质一号, hyperspectral smallsat, co-led with China Aero Geophysical Survey and Remote Sensing Center for Natural Resources
 • Chief engineer Prof. Wang Lizhe) (17 May 2025)
 • Dianjian-1 (电建一号, ~300 kg X-band SAR, led by PowerChina Chengdu Institute, CUG co-developer) (15 May 2026)</t>
         </is>
       </c>
-      <c r="X11" s="4" t="inlineStr">
+      <c r="W11" s="4" t="inlineStr">
         <is>
           <t>• Dizhi-2 (地质二号) hyperspectral satellite (planned
 • Part of a hyperspectral geological constellation concept)</t>
         </is>
       </c>
-      <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="inlineStr">
+      <c r="X11" s="4" t="inlineStr"/>
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>• School of Geophysics and Geomatics / Space Information (地球物理与空间信息学院)
 • School of Earth and Planetary Sciences (地球与行星科学学院)
@@ -7945,7 +7940,7 @@
 • School of Computer Science</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="inlineStr">
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>• China Aero Geophysical Survey and Remote Sensing Center for Natural Resources (MNR/China Geological Survey)
 • Spacety (天仪研究院)
@@ -7954,26 +7949,26 @@
 • PowerChina Chengdu Engineering Corp</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="AD11" s="5" t="inlineStr">
+      <c r="AC11" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE11" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF11" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Самая активная космическая программа в своей группе: Dizhi-1 (2025), Dianjian-1 (2026, совместно с PowerChina)
 • Dizhi-2 в планах
@@ -7981,7 +7976,7 @@
 • Адресат: Адрес cug_global@cug.edu.cn на сайте управления (там только телефоны) не найден — владелец ящика определён по смыслу. Стратегические соглашения ведёт Офис программ совместного обучения (中外合作办学办公室, зам. начальника Fan Luwei 范陆薇)</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cug.edu.cn/xxgk/xrld.htm
 • Https://gjhzc.cug.edu.cn/
@@ -7999,9 +7994,14 @@
 • Https://gjhzc.cug.edu.cn/jgsz/bmld.htm</t>
         </is>
       </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Liu Jie (刘杰)</t>
         </is>
       </c>
     </row>
@@ -8095,71 +8095,66 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>Xiang Changle (项昌乐)</t>
+          <t>QS2027: 463</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 463</t>
+          <t>THE2027: 326–350</t>
         </is>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 326–350</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 28</t>
         </is>
       </c>
-      <c r="V12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>Dalian-1 Lianli (大连1号—连理卫星, 12U CubeSat, launched on Tianzhou-6 2023, released from orbit Jan 2024)</t>
+        </is>
+      </c>
       <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>Dalian-1 Lianli (大连1号—连理卫星, 12U CubeSat, launched on Tianzhou-6 2023, released from orbit Jan 2024)</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>• 12U exoplanet CubeSat concept (Proxima b study
 • Listed as not launched on nanosats.eu)</t>
         </is>
       </c>
-      <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="X12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics (Faculty of Vehicle Engineering and Mechanics)
 • Micro-nano Satellite and Deep Space Exploration team (Prof. Yu Xiaozhou)</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="inlineStr">
+      <c r="Z12" s="4" t="inlineStr">
         <is>
           <t>• China Manned Space Agency (satellite flown via Tianzhou-6 cargo ship)
 • OpenHarmony / OpenAtom Foundation (satellite OS)</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="n">
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD12" s="5" t="inlineStr">
+      <c r="AC12" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE12" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF12" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Президент Гао Сян с октября 2025
 • Международный отдел: dutfao@dlut.edu.cn, +86-411-84706354, факс +86-411-84707983
@@ -8167,7 +8162,7 @@
 • Адресат: dutfao@dlut.edu.cn указан в подвале сайта отдела dutdice.dlut.edu.cn. Личный адрес начальника: wangjue@dlut.edu.cn</t>
         </is>
       </c>
-      <c r="AH12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Https://www.dlut.edu.cn/xxgk/xrld.htm
 • Http://www.news.cn/politics/20251021/d10e8782ff66432aa79cf5eb6f5f7d96/c.html
@@ -8185,9 +8180,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Xiang Changle (项昌乐)</t>
         </is>
       </c>
     </row>
@@ -8285,28 +8285,23 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>Chen Jie (陈杰)</t>
+          <t>QS2027: 190</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 190</t>
+          <t>THE2027: 96</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 96</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 12</t>
         </is>
       </c>
-      <c r="V13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>• HIT reports 46 satellites developed and launched as of Jul 2026
 • Named examples: Shiyan-1 (2004)
@@ -8322,16 +8317,16 @@
 • Zidingxiang-3 / Lilac-3 (2026)</t>
         </is>
       </c>
+      <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="Y13" s="4" t="inlineStr">
         <is>
           <t>• School of Astronautics
 • School of Aeronautics
 • Lilac (Zidingxiang) student micro-nano satellite team</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="inlineStr">
+      <c r="Z13" s="4" t="inlineStr">
         <is>
           <t>• Shijian-26 co-developed with CAST's DFH Satellite Co. and CAS Changchun Institute of Optics (CIOMP)
 • Longjiang-1/2 flew with Chang'e-4 relay mission (CNSA lunar programme)
@@ -8340,31 +8335,31 @@
 • APRU member</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AA13" s="4" t="inlineStr">
         <is>
           <t>Entity List США (с May 2020)
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="n">
+      <c r="AB13" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD13" s="5" t="inlineStr">
+      <c r="AC13" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE13" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF13" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>• Крупнейший вузовский разработчик спутников в Китае: 46 запущенных КА по данным вуза (июль 2026), включая совместные национальные аппараты; полный перечень не опубликован
 • Телефон: отдел управления международным образованием
@@ -8373,7 +8368,7 @@
 • Адресат: Должность «начальник» (部长) на странице не указана, департаментом руководит исполнительный замначальника У Цзянь (jian.wu@hit.edu.cn). В HIT есть отдельный Офис по международным организациям и делам БРИКС (国际组织和金砖事务办公室), руководитель — Сюй Лу (徐璐, xulu@hit.edu.cn): http://international.hit.edu.cn/gjzzhjzswbgs/list.htm. Рекомендуем поставить её в копию</t>
         </is>
       </c>
-      <c r="AH13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>• Https://www.hit.edu.cn/11542/list.htm
 • Https://en.hit.edu.cn/
@@ -8395,9 +8390,14 @@
 • Http://international.hit.edu.cn/16710/list.htm</t>
         </is>
       </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Chen Jie (陈杰)</t>
         </is>
       </c>
     </row>
@@ -8491,80 +8491,75 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>Liu Bo (刘波)</t>
+          <t>QS2027: 307</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 307</t>
+          <t>THE2027: =191</t>
         </is>
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =191</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 9</t>
         </is>
       </c>
-      <c r="V14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W14" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>• TianQin-1 (天琴一号, 2019-12-20
 • Co-developed with Sun Yat-sen University and DFH Satellite Co
 • HUST built the inertial sensing payload)</t>
         </is>
       </c>
-      <c r="X14" s="4" t="inlineStr">
+      <c r="W14" s="4" t="inlineStr">
         <is>
           <t>• TianQin space gravitational-wave constellation (3 satellites ~100,000 km orbit, ~2035
 • SYSU-led programme proposed by HUST academician Luo Jun)</t>
         </is>
       </c>
-      <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr">
         <is>
           <t>• Institute of Digital Aerospace Technology (数字空天技术研究所, est. 2023)
 • TianQin research centre / precision gravitational measurement</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="inlineStr">
+      <c r="Z14" s="4" t="inlineStr">
         <is>
           <t>• TianQin-1 with CAST subsidiary DFH Satellite Co. and Sun Yat-sen University
 • CNSA acceptance of TianQin-1</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="n">
+      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD14" s="5" t="inlineStr">
+      <c r="AC14" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE14" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>• Участие в КА — полезная нагрузка (инерциальный датчик) на TianQin-1; программу TianQin ведёт SYSU
 • Единого международного e-mail нет; адреса сотрудников по регионам
 • Адресат: Начальник управления — Chen Jie (陈洁, 处长). Россия и ЮАР относятся к офису Европы и Африки (курирует зам. начальника Jiang Jing, 江静). Общий ящик управления: international@hust.edu.cn — разумно поставить в копию</t>
         </is>
       </c>
-      <c r="AH14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>• Https://www.hust.edu.cn/xxgk/xrld.htm
 • Https://www.hust.edu.cn/
@@ -8578,9 +8573,14 @@
 • Http://oia.hust.edu.cn/gywm/bmld.htm</t>
         </is>
       </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Liu Bo (刘波)</t>
         </is>
       </c>
     </row>
@@ -8678,28 +8678,23 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>Qiu Yong (邱勇)</t>
+          <t>QS2027: 14</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 14</t>
+          <t>THE2027: 11</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 11</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 1</t>
         </is>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="W15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>• Tsinghua-1 (2000, with SSTL &amp; CASIC)
 • NS-1 / Naxing-1 (2004)
@@ -8707,41 +8702,41 @@
 • Tsinghua Science Satellite (2020, gravity/atmosphere)</t>
         </is>
       </c>
+      <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr">
+      <c r="Y15" s="4" t="inlineStr">
         <is>
           <t>• School of Aerospace Engineering
 • Space Technology Center (宇航技术研究中心)
 • GRID (Tiange) gamma-ray payload project</t>
         </is>
       </c>
-      <c r="AA15" s="4" t="inlineStr">
+      <c r="Z15" s="4" t="inlineStr">
         <is>
           <t>• Tsinghua-1 jointly built with CASIC and University of Surrey/SSTL (Tsinghua-Surrey microsatellite centre)
 • IAF member since 2018</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="n">
+      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="AD15" s="5" t="inlineStr">
+      <c r="AC15" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE15" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF15" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>• КА: 7 к сентябрю 2015 (новости вуза) + Tsinghua Science Satellite (2020) = не менее 8; возможны более поздние запуски
 • Не найден в Entity List США (список Caltech, неполный)
@@ -8749,7 +8744,7 @@
 • Адресат: liaison@ читает Офис по обменам (тел. 62781943/62783293), а общий адрес отдела и руководства — guojichu@tsinghua.edu.cn, его стоит поставить в копию. Пиньинь имени 茜 в именах обычно читается как Qian, на сайте латиницей не указан</t>
         </is>
       </c>
-      <c r="AH15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tsinghua.edu.cn/xxgk/xrld.htm
 • Https://www.tsinghua.edu.cn/en/Contact.htm
@@ -8766,9 +8761,14 @@
 • Https://www.tsinghua.edu.cn/gjhz/gywm/lxwm.htm</t>
         </is>
       </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Qiu Yong (邱勇)</t>
         </is>
       </c>
     </row>
@@ -8866,40 +8866,35 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>Ren Xiaolong (任小龙)</t>
+          <t>QS2027: 851-900</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 851-900</t>
+          <t>THE2027: 601–650</t>
         </is>
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 601–650</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 39</t>
         </is>
       </c>
-      <c r="V16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>Xidian-1 (西电一号, hyperspectral satellite, first of the Zhongxing Silk Road Sky Map constellation, co-developed with China Star Electric/Future Aerospace, 2022)</t>
+        </is>
+      </c>
       <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t>Xidian-1 (西电一号, hyperspectral satellite, first of the Zhongxing Silk Road Sky Map constellation, co-developed with China Star Electric/Future Aerospace, 2022)</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
         <is>
           <t>• Follow-on satellites of the Silk Road Sky Map (丝路天图) remote-sensing constellation (reported as planned
 • Details unverified)</t>
         </is>
       </c>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr">
+      <c r="X16" s="4" t="inlineStr"/>
+      <c r="Y16" s="4" t="inlineStr">
         <is>
           <t>• School of Aerospace Science and Technology (空间科学与技术学院, est. 2013)
 • National Key Laboratory of Antennas and Microwave Technology
@@ -8909,33 +8904,33 @@
 • Qian Xuesen Space Science talent base (with CAST Qian Xuesen Space Technology Lab)</t>
         </is>
       </c>
-      <c r="AA16" s="4" t="inlineStr">
+      <c r="Z16" s="4" t="inlineStr">
         <is>
           <t>• CAST Qian Xuesen Space Technology Laboratory (joint talent base)
 • China Star Electric Aerospace / Future Aerospace (Xidian-1)
 • CASIC Defense Technology Research &amp; Test Center (strategic cooperation, microelectronics school)</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="n">
+      <c r="AA16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="AD16" s="5" t="inlineStr">
+      <c r="AC16" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE16" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF16" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>• Исторически военный вуз связи; в Entity List не найден, но проверять при передаче технологий США
 • Общий e-mail — ящик президента (校长信箱); ящик секретаря парткома sjxx@xidian.edu.cn
@@ -8944,7 +8939,7 @@
 • Адресат: fao@xidian.edu.cn указан в подвале oice.xidian.edu.cn. Личный адрес: ylshen@mail.xidian.edu.cn</t>
         </is>
       </c>
-      <c r="AH16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>• Https://www.xidian.edu.cn/xxgk/xrld.htm
 • Http://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202505/t20250516_1190844.html
@@ -8962,9 +8957,14 @@
 • Https://oice.xidian.edu.cn/gywm/bmgk/zzjg.htm</t>
         </is>
       </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Ren Xiaolong (任小龙)</t>
         </is>
       </c>
     </row>
@@ -9058,36 +9058,31 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>Wang Yunpeng (王云鹏)</t>
+          <t>QS2027: 349</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 349</t>
+          <t>THE2027: =185</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =185</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 11</t>
         </is>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>• Beihang Kongshi-1 / BUAA Air Traffic Satellite-1 (2020, 12U, co-developed with Changsha Tianyi/Spacety)
 • APSCO Student Small Satellite SSS-1 (2021, 36 kg)</t>
         </is>
       </c>
+      <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="inlineStr">
+      <c r="Y17" s="4" t="inlineStr">
         <is>
           <t>• School of Astronautics
 • School of Aeronautic Science and Engineering
@@ -9095,7 +9090,7 @@
 • Regional Centre for Space Science and Technology Education in Asia and the Pacific (China) (RCSSTEAP, UN-affiliated, hosted by Beihang)</t>
         </is>
       </c>
-      <c r="AA17" s="4" t="inlineStr">
+      <c r="Z17" s="4" t="inlineStr">
         <is>
           <t>• APSCO (leads APSCO Student Small Satellite project
 • SSS-1 with participation of Pakistan, Peru etc.)
@@ -9104,31 +9099,31 @@
 • IAF member since 2011</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr">
+      <c r="AA17" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC17" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AD17" s="5" t="inlineStr">
+      <c r="AC17" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE17" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>• 30.09.2026 президент Ван Юньпэн назначен секретарём парткома (вместо Чжао Чанлу); на сайте он указан в обеих должностях — вероятно скорое назначение нового президента, перепроверить перед рассылкой
 • Телефон: International School (бакалавриат)
@@ -9137,7 +9132,7 @@
 • Адресат: На странице international@buaa.edu.cn указан как личный рабочий адрес начальника Бай Линь, так что письмо дойдёт адресату напрямую. К департаменту прикреплены Азиатско-Тихоокеанский региональный центр ООН по космическому образованию (Китай) и учебный центр APSCO, что тематически близко к проекту CubeSat</t>
         </is>
       </c>
-      <c r="AH17" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.buaa.edu.cn/xygk/xxld.htm
 • Https://www.sohu.com/a/1082601837_121019331
@@ -9157,9 +9152,14 @@
 • Https://global.buaa.edu.cn/gywm/zzjg.htm</t>
         </is>
       </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Wang Yunpeng (王云鹏)</t>
         </is>
       </c>
     </row>
@@ -9251,66 +9251,61 @@
           <t>President</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>Xu Huarui (徐华瑞)</t>
-        </is>
-      </c>
+      <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>BCUR2026: 86</t>
         </is>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="W18" s="4" t="inlineStr">
+      <c r="V18" s="4" t="inlineStr">
         <is>
           <t>• CXPD-01 (1U X-ray polarimetry CubeSat, 2023-06-07, Lijian-1)
 • CXPD-03 &amp; CXPD-04 (2025-05-14, with Zhejiang Lab Three-Body Computing Constellation)
 • CXPD-02 (2025-05-17, Zhuque-2E)</t>
         </is>
       </c>
-      <c r="X18" s="4" t="inlineStr">
+      <c r="W18" s="4" t="inlineStr">
         <is>
           <t>Next-generation low-energy polarisation detector for the China Space Station (POLAR-2)</t>
         </is>
       </c>
-      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="X18" s="4" t="inlineStr"/>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>School of Physical Science and Technology (物理科学与工程技术学院), CXPD collaboration lead</t>
+        </is>
+      </c>
       <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>School of Physical Science and Technology (物理科学与工程技术学院), CXPD collaboration lead</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
         <is>
           <t>• CXPD collaboration with CAS Institute of High Energy Physics, University of CAS, Central China Normal University and Beijing Institute of Spacecraft Environment Engineering (CAST)
 • Zhejiang Lab Three-Body Computing Constellation
 • POLAR-2 on China Space Station</t>
         </is>
       </c>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="n">
+      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AD18" s="5" t="inlineStr">
+      <c r="AC18" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD18" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE18" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF18" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>• Активная программа кубсатов: 4 рентгеновских поляриметра на орбите с 2023
 • Нет в рейтингах THE 2027 и QS 2027 (топ-500)
@@ -9318,7 +9313,7 @@
 • Адресат: Сайт отдела переехал на gjjl.gxu.edu.cn; gjc@gxu.edu.cn указан там как официальный e-mail отдела</t>
         </is>
       </c>
-      <c r="AH18" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>• Https://www.gxu.edu.cn/en/About_GX/Current_Administrators.htm
 • Https://www.gxu.edu.cn/en/info/1204/2095.htm
@@ -9330,9 +9325,14 @@
 • Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking</t>
         </is>
       </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Xu Huarui (徐华瑞)</t>
         </is>
       </c>
     </row>
@@ -9411,68 +9411,63 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>He Yaqiong (何亚琼)</t>
+          <t>QS2027: 721-730</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 721-730</t>
+          <t>THE2027: 651-700</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 651-700</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 37</t>
         </is>
       </c>
-      <c r="V19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W19" s="4" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>• Tianxun-1 / TX-1 (2011, 60 kg microsat)
 • Zhizhou tethered satellite (2026, launched with Tianzhou-10)</t>
         </is>
       </c>
+      <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="4" t="inlineStr">
+      <c r="Y19" s="4" t="inlineStr">
         <is>
           <t>• College of Astronautics
 • College of Aerospace Engineering (incl. Intelligent Equipment Dynamics Center)</t>
         </is>
       </c>
-      <c r="AA19" s="4" t="inlineStr">
+      <c r="Z19" s="4" t="inlineStr">
         <is>
           <t>• Zhizhou flew on Tianzhou-10 cargo mission (China Manned Space programme)
 • IAF member since 2019</t>
         </is>
       </c>
-      <c r="AB19" s="4" t="inlineStr">
+      <c r="AA19" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC19" s="4" t="n">
+      <c r="AB19" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="AD19" s="5" t="inlineStr">
+      <c r="AC19" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="inlineStr"/>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
       <c r="AF19" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>• Новый секретарь парткома Хэ Яцюн с июня 2026
 • Сайт международного отдела (iao.nuaa.edu.cn) был недоступен — e-mail не подтверждён
@@ -9480,7 +9475,7 @@
 • Адресат: Официального e-mail отдела на сайте ico.nuaa.edu.cn не нашли, там есть только телефоны (общий: 025-84890911, начальник: 025-84891458, факс 025-84498069). Вопросы международных связей ведёт замначальника Чжан Гоцюань (张国权), а вопросы общего сектора — его руководитель Цзу Юйянь (祖语嫣). E-mail нужно уточнить по телефону</t>
         </is>
       </c>
-      <c r="AH19" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nuaa.edu.cn/481/list.htm
 • Https://news.sciencenet.cn/htmlnews/2026/6/566759.shtm
@@ -9498,9 +9493,14 @@
 • Http://ico.nuaa.edu.cn/10476/list.htm</t>
         </is>
       </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>He Yaqiong (何亚琼)</t>
         </is>
       </c>
     </row>
@@ -9598,43 +9598,38 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Jiang Hong (姜虹)</t>
+          <t>QS2027: 317</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 317</t>
+          <t>THE2027: =163</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =163</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 30</t>
         </is>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W20" s="4" t="inlineStr">
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>• Nanke-1 (南科一号 / Tianyi-34, SUSTech electric-field &amp; aurora-camera payloads, 2025)
 • Pengcheng Nanke-1 / PEGA-SUS 1 (鹏城南科一号, 5G NTN satellite with Peng Cheng Lab and GalaxySpace, SUSTech-led comms payload, 2026)</t>
         </is>
       </c>
+      <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="4" t="inlineStr">
+      <c r="Y20" s="4" t="inlineStr">
         <is>
           <t>• Department of Earth and Space Sciences (space physics
 • Electric-field and auroral instruments)
 • Department of Electronic and Electrical Engineering – Electromagnetic Information Lab</t>
         </is>
       </c>
-      <c r="AA20" s="4" t="inlineStr">
+      <c r="Z20" s="4" t="inlineStr">
         <is>
           <t>• Peng Cheng Laboratory
 • GalaxySpace
@@ -9643,26 +9638,26 @@
 • Guangzhou Chengxing Communications</t>
         </is>
       </c>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="n">
+      <c r="AA20" s="4" t="inlineStr"/>
+      <c r="AB20" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AD20" s="5" t="inlineStr">
+      <c r="AC20" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD20" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE20" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF20" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Платформы КА построены партнёрами (Tianyi, GalaxySpace/Peng Cheng Lab); вуз разработал полезные нагрузки
 • Один факультет в Unverified List (UVL) США — не Entity List
@@ -9671,7 +9666,7 @@
 • Адресат: global@sustech.edu.cn — «公共邮箱» департамента. Должность начальника (部长) на сайте не указана; Чэнь Хао значится как «部门负责人» (руководитель подразделения)</t>
         </is>
       </c>
-      <c r="AH20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sustech.edu.cn/zh/leadership.html
 • Https://news.eol.cn/dongtai/gxrs/202307/t20230701_2450265.shtml
@@ -9687,9 +9682,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Jiang Hong (姜虹)</t>
         </is>
       </c>
     </row>
@@ -9777,68 +9777,67 @@
           <t>President</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 243</t>
+        </is>
+      </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 243</t>
+          <t>THE2027: 234</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 234</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 14</t>
         </is>
       </c>
-      <c r="V21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W21" s="4" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>CAS-7B / BP-1 'Bei Ligong 1 hao' / BIT Progress-OSCAR 102 (2019, with CAMSAT)</t>
         </is>
       </c>
+      <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
-      <c r="Y21" s="4" t="inlineStr"/>
+      <c r="Y21" s="4" t="inlineStr">
+        <is>
+          <t>School of Aerospace Science and Technology (空天科学与技术学院)</t>
+        </is>
+      </c>
       <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>School of Aerospace Science and Technology (空天科学与技术学院)</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr">
         <is>
           <t>• CAMSAT (CAS-7B amateur satellite)
 • Participation in crewed spaceflight, BeiDou and Mars exploration programmes (per university profile)</t>
         </is>
       </c>
-      <c r="AB21" s="4" t="inlineStr">
+      <c r="AA21" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC21" s="4" t="n">
+      <c r="AB21" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AD21" s="5" t="inlineStr">
+      <c r="AC21" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE21" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF21" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>• Срок секретаря парткома Чжан Цзюня истёк в июле 2026; преемник на сайте не указан
 • Телефон: отдел международного сотрудничества; приёмная президента/парткома +86-10-68914247
@@ -9847,7 +9846,7 @@
 • Адресат: Общего e-mail отдела на сайте нет, найдены только личные адреса сотрудников. Начальник отдела — Чэнь Дуаньдуань (陈端端, 处长), см. https://international.bit.edu.cn/gywm/ksry/cld/index.htm. Её e-mail не опубликован. Можно адресовать письмо ей («Dear Director Chen,») и отправить через zongxin@. Данные поисковика о начальнике «Тан Шуйюань» устарели</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bit.edu.cn/gbxxgk/xxld_sjb/index.htm
 • Https://www.bit.edu.cn/gbxxgk/xxld_sjb/25b42cea6c414fdb9b2d05c0d04169fc.htm
@@ -9863,11 +9862,12 @@
 • Https://international.bit.edu.cn/gywm/ksry/jlhzs/index.htm</t>
         </is>
       </c>
-      <c r="AI21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
+      <c r="AI21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -9955,73 +9955,68 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Tan Tieniu (谭铁牛)</t>
+          <t>QS2027: 90</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 90</t>
+          <t>THE2027: 59</t>
         </is>
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 59</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 6</t>
         </is>
       </c>
-      <c r="V22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W22" s="4" t="inlineStr">
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>• Nanda-1 / Lobster-eye X-ray Detection Satellite (南大一号/龙虾眼X射线探测卫星, 2020-07-25). Also: science lead/participant in CHASE 'Xihe' solar satellite (2021-10-14)
 • NJU video remote-sensing payload launched on Kuaizhou-11 Y8 (2025-12-13)</t>
         </is>
       </c>
+      <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
-      <c r="Y22" s="4" t="inlineStr"/>
+      <c r="Y22" s="4" t="inlineStr">
+        <is>
+          <t>School of Astronomy and Space Science</t>
+        </is>
+      </c>
       <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>School of Astronomy and Space Science</t>
-        </is>
-      </c>
-      <c r="AA22" s="4" t="inlineStr">
         <is>
           <t>• Lobster-eye satellite with HKU Laboratory for Space Research, CAST (CASC 5th Academy) Institute 508 and SAST 805 subsidiary ASES
 • Xihe (CHASE) solar mission with CNSA</t>
         </is>
       </c>
-      <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="n">
+      <c r="AA22" s="4" t="inlineStr"/>
+      <c r="AB22" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AD22" s="5" t="inlineStr">
+      <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD22" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE22" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF22" s="4" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>• Сильный пользователь космических данных (рентгеновская астрономия, физика Солнца)
 • Опубликован только webmaster@nju.edu.cn; международный e-mail не подтверждён (по поиску stuex@nju.edu.cn)
 • Адресат: oice@nju.edu.cn — официальный ящик управления (подвал сайта wb.nju.edu.cn). Личный e-mail начальника alu@nju.edu.cn; по межвузовским проектам — Chen Nan (陈楠, chennan@nju.edu.cn, начальник офиса обменов и проектов)</t>
         </is>
       </c>
-      <c r="AH22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nju.edu.cn/ndgk/xrld.htm
 • Https://njunju.nju.edu.cn/EN/administrative_offices/list.htm
@@ -10034,9 +10029,14 @@
 • Https://wb.nju.edu.cn/jgsz/list.htm</t>
         </is>
       </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Tan Tieniu (谭铁牛)</t>
         </is>
       </c>
     </row>
@@ -10135,36 +10135,31 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>Li Zhongjun (李忠军)</t>
+          <t>QS2027: 309</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 309</t>
+          <t>THE2027: =263</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =263</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 22</t>
         </is>
       </c>
-      <c r="V23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W23" s="4" t="inlineStr">
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>• Weiming-1 / Mofulong (未名一号/默孚龙号, ~30 kg, co-developed by PKU, SDU and MinoSpace
 • SDU built neutron spectrometer and Langmuir probe payloads) (Jan 2024)</t>
         </is>
       </c>
+      <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="4" t="inlineStr"/>
-      <c r="Z23" s="4" t="inlineStr">
+      <c r="Y23" s="4" t="inlineStr">
         <is>
           <t>• Institute of Space Sciences / School of Space Science and Physics (空间科学研究院 / 空间科学与物理学院, Weihai)
 • Space Science Climbing Team
@@ -10172,32 +10167,32 @@
 • School of Mechanical, Electrical and Information Engineering (Weihai)</t>
         </is>
       </c>
-      <c r="AA23" s="4" t="inlineStr">
+      <c r="Z23" s="4" t="inlineStr">
         <is>
           <t>• Peking University and MinoSpace (Weiming-1 joint satellite)
 • Listed in China University Planetary Science Alliance navbox (Wikipedia)</t>
         </is>
       </c>
-      <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="n">
+      <c r="AA23" s="4" t="inlineStr"/>
+      <c r="AB23" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AD23" s="5" t="inlineStr">
+      <c r="AC23" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE23" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF23" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• 1 КА: Weiming-1 совместно с PKU и MinoSpace; вклад вуза — 2 полезные нагрузки
 • Космический центр — кампус Вэйхай (fxipo@wh.sdu.edu.cn, +86-631-5688016)
@@ -10205,7 +10200,7 @@
 • Адресат: Личный e-mail: mawen@sdu.edu.cn. Сотрудничество с Россией и ШОС курирует зам. руководителя Zhou Chuan'en (周传恩), czhou@sdu.edu.cn; международные обмены в целом — Zhang Jiaqi (张佳琦), jqzhang@sdu.edu.cn</t>
         </is>
       </c>
-      <c r="AH23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sdu.edu.cn/sdgk/xrld.htm
 • Https://www.en.sdu.edu.cn/Contact_Us.htm
@@ -10217,9 +10212,14 @@
 • Https://www.ipo.sdu.edu.cn/bmjk/ryfg.htm</t>
         </is>
       </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Li Zhongjun (李忠军)</t>
         </is>
       </c>
     </row>
@@ -10309,70 +10309,65 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Cao Ping (曹萍)</t>
+          <t>QS2027: 488</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 488</t>
+          <t>THE2027: 351–375</t>
         </is>
       </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 351–375</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 33</t>
         </is>
       </c>
-      <c r="V24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W24" s="4" t="inlineStr">
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>UESTC-sat / 'Dianzi Keji Daxue hao' (电子科技大学号, Xingshidai-12 / Tianyan-05, 6G terahertz test satellite co-developed with ADASpace, 2020)</t>
         </is>
       </c>
+      <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="4" t="inlineStr"/>
+      <c r="Y24" s="4" t="inlineStr">
+        <is>
+          <t>School of Aeronautics and Astronautics (Institute of Aerospace Science and Technology): Navigation, Guidance &amp; TT&amp;C Research Center, Optical Communication Research Center, space microwave and space laser communication groups</t>
+        </is>
+      </c>
       <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>School of Aeronautics and Astronautics (Institute of Aerospace Science and Technology): Navigation, Guidance &amp; TT&amp;C Research Center, Optical Communication Research Center, space microwave and space laser communication groups</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="inlineStr">
         <is>
           <t>• ADASpace (Guoxing Aerospace) – 6G test satellite
 • Huantian Smart Technology (naming of Chengdian-1, 2026)
 • Applications in China's crewed spaceflight programme (per school profile)</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr">
+      <c r="AA24" s="4" t="inlineStr">
         <is>
           <t>Entity List США</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="n">
+      <c r="AB24" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="AD24" s="5" t="inlineStr">
+      <c r="AC24" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE24" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF24" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• В Entity List США (с 2012)
 • Chengdian-1 (март 2026) носит имя вуза, но построен компанией Huantian — не учтён
@@ -10381,7 +10376,7 @@
 • Адресат: zhaoban@uestc.edu.cn — ящик приёмной комиссии (招生办), для партнёрского письма не подходит. international@uestc.edu.cn взят из выдачи поиска по en.uestc.edu.cn/index/Contact_Us.htm, но саму страницу открыть не удалось (JS-защита) — проверить. Сайт отдела oice.uestc.edu.cn закрыт антиботом; имя начальника не подтверждено (в поиске встречаются разные имена: 高世全, 邸爱英)</t>
         </is>
       </c>
-      <c r="AH24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uestc.edu.cn/xxgk/xrld.htm
 • Http://www.xinhuanet.com/edu/20240223/1119ae399c4d48ecb0f7932a54fe9182/c.html
@@ -10398,9 +10393,14 @@
 • Https://researchpolicy.caltech.edu/research-security/international_collaboration/restricted-party-screening/foreign-universities-sanctioned-by-the-us-government</t>
         </is>
       </c>
+      <c r="AH24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Cao Ping (曹萍)</t>
         </is>
       </c>
     </row>
@@ -10494,11 +10494,10 @@
       <c r="R25" s="4" t="inlineStr"/>
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="W25" s="4" t="inlineStr">
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>• Tiantuo-1 (2012)
 • Tiantuo-2 (2014, video microsat)
@@ -10507,42 +10506,42 @@
 • Tiantuo-5 (2020, 78.5 kg)</t>
         </is>
       </c>
+      <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="4" t="inlineStr"/>
+      <c r="Y25" s="4" t="inlineStr">
+        <is>
+          <t>College of Aerospace Science and Engineering (空天科学学院)</t>
+        </is>
+      </c>
       <c r="Z25" s="4" t="inlineStr">
         <is>
-          <t>College of Aerospace Science and Engineering (空天科学学院)</t>
+          <t>QB50 (NUDTSat)</t>
         </is>
       </c>
       <c r="AA25" s="4" t="inlineStr">
         <is>
-          <t>QB50 (NUDTSat)</t>
-        </is>
-      </c>
-      <c r="AB25" s="4" t="inlineStr">
-        <is>
           <t>Entity List США</t>
         </is>
       </c>
-      <c r="AC25" s="4" t="n">
+      <c r="AB25" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AD25" s="5" t="inlineStr">
+      <c r="AC25" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD25" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE25" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF25" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>• Военный вуз НОАК — не входит в рейтинги QS/THE/BCUR; участие в гражданской группировке маловероятно
 • Вместо секретаря парткома — политкомиссар; имя не подтверждено
@@ -10552,7 +10551,7 @@
 • Адресат: Военный вуз (НОАК), состав руководства отдела иностранных дел не публикуется. Адрес fao@nudt.edu.cn подтверждён в контактах англоязычного сайта (тел. +86-731-87000275). Имя руководителя установить нельзя. Учтите, что университет включён в санкционные списки США (Entity List)</t>
         </is>
       </c>
-      <c r="AH25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>• Https://news.eol.cn/dongtai/gxrs/202606/t20260629_2750325.shtml
 • Https://english.nudt.edu.cn/
@@ -10566,11 +10565,12 @@
 • Nanosats.eu export (local nanosats.csv)</t>
         </is>
       </c>
-      <c r="AI25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
+      <c r="AI25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -10643,62 +10643,57 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Lu Guibin (路贵斌)</t>
+          <t>QS2027: 675</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 675</t>
+          <t>THE2027: 551-600</t>
         </is>
       </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 551-600</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 36</t>
         </is>
       </c>
-      <c r="V26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W26" s="4" t="inlineStr">
+      <c r="V26" s="4" t="inlineStr">
         <is>
           <t>• NJUST-1, QB50 BE03 (2017)
 • Tianyuan-1, 6U (2021)</t>
         </is>
       </c>
+      <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
-      <c r="Z26" s="4" t="inlineStr"/>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
+          <t>QB50 (NJUST-1)</t>
+        </is>
+      </c>
       <c r="AA26" s="4" t="inlineStr">
-        <is>
-          <t>QB50 (NJUST-1)</t>
-        </is>
-      </c>
-      <c r="AB26" s="4" t="inlineStr">
         <is>
           <t>Entity List США
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC26" s="4" t="n">
+      <c r="AB26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AD26" s="5" t="inlineStr">
+      <c r="AC26" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AE26" s="4" t="inlineStr">
+        <is>
+          <t>низкая</t>
+        </is>
+      </c>
       <c r="AF26" s="4" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>• Сайт njust.edu.cn закрыт антибот-защитой — страницы руководства и контактов не открылись
 • Руководство взято из китайской Википедии, не подтверждено на 2025–2026 — перепроверить
@@ -10706,7 +10701,7 @@
 • Адресат: Сайты njust.edu.cn (включая gjc.njust.edu.cn и english.njust.edu.cn) закрыты анти-бот защитой (JS-челлендж), страницы прочитать не удалось. Ни e-mail отдела, ни имя начальника подтвердить нельзя, нужно проверить вручную в браузере</t>
         </is>
       </c>
-      <c r="AH26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Nanjing_University_of_Science_and_Technology
 • Https://zh.wikipedia.org/zh-cn/南京理工大学
@@ -10720,9 +10715,14 @@
 • Https://gjc.njust.edu.cn/</t>
         </is>
       </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Lu Guibin (路贵斌)</t>
         </is>
       </c>
     </row>
@@ -10816,35 +10816,30 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>Tian Hui (田辉)</t>
+          <t>QS2027: 488</t>
         </is>
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 488</t>
+          <t>THE2027: 376-400</t>
         </is>
       </c>
       <c r="T27" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 376-400</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 26</t>
         </is>
       </c>
-      <c r="V27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W27" s="4" t="inlineStr">
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>Jilin University-1 / Jitianxing A-01 (吉林大学一号/吉天星A-01星, metre-class push-broom optical remote-sensing satellite, Jielong-3, 24 Sep 2024)</t>
         </is>
       </c>
+      <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="4" t="inlineStr"/>
-      <c r="Z27" s="4" t="inlineStr">
+      <c r="Y27" s="4" t="inlineStr">
         <is>
           <t>• College of Instrumentation and Electrical Engineering (仪器科学与电气工程学院, led the satellite
 • Zhang Liu team under Academician Lin Jun)
@@ -10852,27 +10847,27 @@
 • College of Geo-Exploration Science and Technology</t>
         </is>
       </c>
+      <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="n">
+      <c r="AB27" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AD27" s="5" t="inlineStr">
+      <c r="AC27" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE27" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF27" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• Новый секретарь парткома Тянь Хуэй (ранее Цзян Чжиин)
 • КА Jilin University-1 (2024): первый снимок через 38 ч после запуска; второй КА не подтверждён
@@ -10881,7 +10876,7 @@
 • Адресат: Служебный ящик директора: director_global@jlu.edu.cn (можно поставить в копию). Сотрудничество/платформы курирует зам. начальника Gao Yixing (高一星), gaoyixing@jlu.edu.cn</t>
         </is>
       </c>
-      <c r="AH27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• Https://www.jlu.edu.cn/xxgk/xrld.htm
 • Https://oic.jlu.edu.cn/
@@ -10896,9 +10891,14 @@
 • Http://oic.jlu.edu.cn/gywm/bmld.htm</t>
         </is>
       </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Tian Hui (田辉)</t>
         </is>
       </c>
     </row>
@@ -10990,57 +10990,52 @@
           <t>President</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr">
-        <is>
-          <t>Li Ruxin (李儒新)</t>
-        </is>
-      </c>
+      <c r="R28" s="4" t="inlineStr"/>
       <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="inlineStr">
+      <c r="T28" s="4" t="inlineStr">
         <is>
           <t>BCUR2026: 47</t>
         </is>
       </c>
-      <c r="V28" s="4" t="n">
+      <c r="U28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W28" s="4" t="inlineStr">
+      <c r="V28" s="4" t="inlineStr">
         <is>
           <t>• STU-2A/2B/2C (上科大二号, three CubeSats aka TW-1A/B/C, 2015-09-25, Long March 11
 • Developed by Shanghai Engineering Centre for Microsatellites with ShanghaiTech). STU-1 (QB50) was cancelled</t>
         </is>
       </c>
+      <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
-      <c r="Z28" s="4" t="inlineStr"/>
-      <c r="AA28" s="4" t="inlineStr">
+      <c r="Z28" s="4" t="inlineStr">
         <is>
           <t>• Co-founded by Shanghai Municipal Government and Chinese Academy of Sciences
 • Science-education partnership with Shanghai Engineering Centre for Microsatellites / CAS Innovation Academy for Microsatellites (SECM/IAMCAS)
 • Former QB50 participant (STU-1, cancelled)</t>
         </is>
       </c>
-      <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="n">
+      <c r="AA28" s="4" t="inlineStr"/>
+      <c r="AB28" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="AD28" s="5" t="inlineStr">
+      <c r="AC28" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
+      <c r="AD28" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE28" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF28" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>• КА STU-2 носят имя вуза, но построены SECM (CAS); роль вуза — научное и образовательное использование
 • Связь с CAS — выход на экспертизу IAMCAS по микроспутникам
@@ -11048,7 +11043,7 @@
 • Адресат: Должности начальника нет — управлением руководит зам. начальника Nie Yan (nieyan@shanghaitech.edu.cn). Международными программами занимается Xiao Yin (肖茵, помощник начальника, xiaoyin@shanghaitech.edu.cn) — можно в копию</t>
         </is>
       </c>
-      <c r="AH28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>• Https://www.shanghaitech.edu.cn/2025/1223/c1584a1118320/page.htm
 • Http://www.shanghaitech.edu.cn/en/1059/list.htm
@@ -11060,9 +11055,14 @@
 • Https://oia.shanghaitech.edu.cn/549/list.htm</t>
         </is>
       </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Li Ruxin (李儒新)</t>
         </is>
       </c>
     </row>
@@ -11156,67 +11156,62 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>Li Ming (李明)</t>
+          <t>QS2027: 801-850</t>
         </is>
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 801-850</t>
+          <t>THE2027: 601-650</t>
         </is>
       </c>
       <c r="T29" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 601-650</t>
-        </is>
-      </c>
-      <c r="U29" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 51</t>
         </is>
       </c>
-      <c r="V29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="4" t="inlineStr"/>
-      <c r="X29" s="4" t="inlineStr">
+      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="inlineStr">
         <is>
           <t>• Guanlan (观澜号) ocean science satellite: interferometric imaging altimeter and ocean lidar. Design project led by OUC under the Aoshan programme, launched May 2018
 • Launch status not found</t>
         </is>
       </c>
-      <c r="Y29" s="4" t="inlineStr"/>
-      <c r="Z29" s="4" t="inlineStr">
+      <c r="X29" s="4" t="inlineStr"/>
+      <c r="Y29" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Information Science and Engineering (信息科学与工程学部, ocean remote sensing)
 • College of Oceanic and Atmospheric Sciences
 • Key Laboratory of Physical Oceanography (MoE)</t>
         </is>
       </c>
-      <c r="AA29" s="4" t="inlineStr">
+      <c r="Z29" s="4" t="inlineStr">
         <is>
           <t>Guanlan project partners included Qingdao National Laboratory for Marine Science and Technology (Laoshan Lab), CASC 5th and 8th Academies (CAST/SAST), CAS National Space Science Center, CASIC 2nd Academy 23rd Institute, CETC 38th Institute, CAS AIR (per 2018 kickoff report)</t>
         </is>
       </c>
-      <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="n">
+      <c r="AA29" s="4" t="inlineStr"/>
+      <c r="AB29" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="AD29" s="6" t="inlineStr">
+      <c r="AC29" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE29" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF29" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>• Запущенных КА нет; в разработке океанографический КА Guanlan (гл. научный сотрудник проф. Чэнь Гэ)
 • Региональные контакты: wanqian@ouc.edu.cn (Европа), +86-532-66786570
@@ -11224,7 +11219,7 @@
 • Адресат: На сайте intl.ouc.edu.cn нет страницы руководства; должность подтверждена новостью ОУК от 30.09.2026 (и визитом в Нанкинский университет 03.03.2026). Адрес international@ouc.edu.cn на открытых страницах не встретился — не перепроверен</t>
         </is>
       </c>
-      <c r="AH29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ouc.edu.cn/31003/list.htm
 • Http://eweb.ouc.edu.cn/2851/list.htm
@@ -11239,9 +11234,14 @@
 • Http://news.ouc.edu.cn/2026/0930/c78a122866/page.htm</t>
         </is>
       </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Li Ming (李明)</t>
         </is>
       </c>
     </row>
@@ -11335,31 +11335,26 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>An Shi (安实)</t>
+          <t>QS2027: 452</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 452</t>
+          <t>THE2027: =277</t>
         </is>
       </c>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =277</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 27</t>
         </is>
       </c>
-      <c r="V30" s="4" t="n">
+      <c r="U30" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
-      <c r="Y30" s="4" t="inlineStr"/>
-      <c r="Z30" s="4" t="inlineStr">
+      <c r="Y30" s="4" t="inlineStr">
         <is>
           <t>• Institute of Aerospace Technology (航空航天技术研究院, within School of Mechanical and Electrical Engineering)
 • School of Aeronautics and Astronautics (listed on English site)
@@ -11367,31 +11362,31 @@
 • Powder Metallurgy Research Institute (C/C composites for FY-4 satellite)</t>
         </is>
       </c>
-      <c r="AA30" s="4" t="inlineStr">
+      <c r="Z30" s="4" t="inlineStr">
         <is>
           <t>Supplied C/C composite sun-shield components for the Fengyun-4 meteorological satellite (2016)</t>
         </is>
       </c>
-      <c r="AB30" s="4" t="inlineStr"/>
-      <c r="AC30" s="4" t="n">
+      <c r="AA30" s="4" t="inlineStr"/>
+      <c r="AB30" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AD30" s="6" t="inlineStr">
+      <c r="AC30" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="AD30" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE30" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF30" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>• Собственных КА нет; космическая тематика — материалы для РН и КА
 • Страница контактов международного отдела без e-mail; указан адрес службы иностранных студентов
@@ -11399,7 +11394,7 @@
 • Адресат: admissions@csu.edu.cn — приём иностранных студентов, не для партнёрств. На странице контактов 国际处 для «交流项目» указан ied-csu@csu.edu.cn; отдел обменов отвечает за переговоры и соглашения с зарубежными вузами (зам. руководителя отдела — Wen Ning 文宁). Руководство: https://iecd.csu.edu.cn/gywm/jgsz.htm</t>
         </is>
       </c>
-      <c r="AH30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.csu.edu.cn/zjzn/xxld.htm
 • Https://en.csu.edu.cn/index/Contact.htm
@@ -11413,9 +11408,14 @@
 • Https://iecd.csu.edu.cn/gywm/lxwm.htm</t>
         </is>
       </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>An Shi (安实)</t>
         </is>
       </c>
     </row>
@@ -11509,63 +11509,58 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>He Guangcai (何光彩)</t>
+          <t>QS2027: 13</t>
         </is>
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 13</t>
+          <t>THE2027: 13</t>
         </is>
       </c>
       <c r="T31" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 13</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 2</t>
         </is>
       </c>
-      <c r="V31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
-      <c r="Y31" s="4" t="inlineStr"/>
-      <c r="Z31" s="4" t="inlineStr">
+      <c r="Y31" s="4" t="inlineStr">
         <is>
           <t>• School of Earth and Space Sciences (Institute of Space Physics and Applied Technology
 • Institute of Remote Sensing and GIS)
 • Payload development (energetic particle detectors, neutral atom imagers, boom-less magnetometers)</t>
         </is>
       </c>
-      <c r="AA31" s="4" t="inlineStr">
+      <c r="Z31" s="4" t="inlineStr">
         <is>
           <t>• Space particle/magnetic-field payload (with Shandong University) flown on MinoSpace Taijing-2 04 (2024)
 • Co-developer partner in BUPT-led Tiansuan constellation / BUPT-1</t>
         </is>
       </c>
-      <c r="AB31" s="4" t="inlineStr"/>
-      <c r="AC31" s="4" t="n">
+      <c r="AA31" s="4" t="inlineStr"/>
+      <c r="AB31" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AD31" s="6" t="inlineStr">
+      <c r="AC31" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="AD31" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE31" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF31" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>• Президент Гао Сун с 23.05.2026; секретарь парткома Хэ Гуанцай с февраля 2025
 • Собственных КА нет; сильные стороны — научные полезные нагрузки
@@ -11573,7 +11568,7 @@
 • Адресат: outreach@pku.edu.cn подтверждён на www.oir.pku.edu.cn/home/Contact_Us/Contact_Us.htm как адрес Office of International Relations. Страница прочитана через WebFetch (curl блокирован); личный адрес: liyun@pku.edu.cn</t>
         </is>
       </c>
-      <c r="AH31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>• Https://www.news.cn/politics/20260523/28ec306ae108409f88924b9d2f2b1520/c.html
 • Https://www.pku.edu.cn/leaders.html
@@ -11590,9 +11585,14 @@
 • Http://www.oir.pku.edu.cn/gywm.htm</t>
         </is>
       </c>
+      <c r="AH31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>He Guangcai (何光彩)</t>
         </is>
       </c>
     </row>
@@ -11686,65 +11686,60 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Gan Lin (甘霖)</t>
+          <t>QS2027: 300</t>
         </is>
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 300</t>
+          <t>THE2027: =224</t>
         </is>
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =224</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 16</t>
         </is>
       </c>
-      <c r="V32" s="4" t="n">
+      <c r="U32" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
-      <c r="Y32" s="4" t="inlineStr"/>
-      <c r="Z32" s="4" t="inlineStr">
+      <c r="Y32" s="4" t="inlineStr">
         <is>
           <t>• School of Aeronautics and Astronautics (空天科学与工程学院)
 • College of Physics GRID (天格计划) student team</t>
         </is>
       </c>
+      <c r="Z32" s="4" t="inlineStr">
+        <is>
+          <t>GRID (Gamma-Ray Integrated Detectors) consortium with Tsinghua University (GRID-11B co-developed, flown on Chang Guang Satellite Jilin-1 platform 02A03, 11 Nov 2024)</t>
+        </is>
+      </c>
       <c r="AA32" s="4" t="inlineStr">
         <is>
-          <t>GRID (Gamma-Ray Integrated Detectors) consortium with Tsinghua University (GRID-11B co-developed, flown on Chang Guang Satellite Jilin-1 platform 02A03, 11 Nov 2024)</t>
-        </is>
-      </c>
-      <c r="AB32" s="4" t="inlineStr">
-        <is>
           <t>Entity List США</t>
         </is>
       </c>
-      <c r="AC32" s="4" t="n">
+      <c r="AB32" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AD32" s="6" t="inlineStr">
+      <c r="AC32" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE32" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF32" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>• В Entity List США (2012, обновлено 2023) — проверить экспортные ограничения
 • Собственных КА нет; гамма-детекторы GRID на чужих КА (4 нагрузки на орбите) — не учтены
@@ -11752,7 +11747,7 @@
 • Адресат: Официальная англ. страница контактов указывает «Zhiqiang Li, Director of International Office», e-mail international@scu.edu.cn (общий для всего руководства). Иероглифы 李志强 взяты из поиска (по нему он также декан Школы международных отношений и русист) — китайский сайт global.scu.edu.cn недоступен для проверки; футер англ. страницы © 2020</t>
         </is>
       </c>
-      <c r="AH32" s="4" t="inlineStr">
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>• Https://www.scu.edu.cn/xxgk/ldjg.htm
 • Https://international.scu.edu.cn/About_Us/Contact_Us/Contact_Us.htm
@@ -11765,9 +11760,14 @@
 • Https://www.ecfr.gov/current/title-15/part-744/appendix-Supplement%20No.%204%20to%20Part%20744</t>
         </is>
       </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Gan Lin (甘霖)</t>
         </is>
       </c>
     </row>
@@ -11857,63 +11857,58 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>Zheng Qinghua (郑庆华)</t>
+          <t>QS2027: 146</t>
         </is>
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 146</t>
+          <t>THE2027: 124</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 124</t>
-        </is>
-      </c>
-      <c r="U33" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 18</t>
         </is>
       </c>
-      <c r="V33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
-      <c r="Y33" s="4" t="inlineStr"/>
-      <c r="Z33" s="4" t="inlineStr">
+      <c r="Y33" s="4" t="inlineStr">
         <is>
           <t>• School of Aerospace Engineering and Applied Mechanics (航空航天与力学学院)
 • College of Surveying and Geo-Informatics (测绘与地理信息学院)
 • MoE Deep Space Exploration Joint Research Center - Tongji Sub-center for Deep-Space Mapping, Remote Sensing and Navigation/Positioning (深空探测测绘遥感与导航定位分中心)</t>
         </is>
       </c>
-      <c r="AA33" s="4" t="inlineStr">
+      <c r="Z33" s="4" t="inlineStr">
         <is>
           <t>• MoE Deep Space Exploration Joint Research Center sub-center supporting lunar/Mars exploration (serves CASC per centre description)
 • Listed in China University Planetary Science Alliance navbox (Wikipedia)</t>
         </is>
       </c>
-      <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="n">
+      <c r="AA33" s="4" t="inlineStr"/>
+      <c r="AB33" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AD33" s="6" t="inlineStr">
+      <c r="AC33" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="AD33" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE33" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF33" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>• Собственных КА нет
 • Отдел внешних связей публикует только телефон, без e-mail
@@ -11922,7 +11917,7 @@
 • Адресат: outreach_email был пуст. wsbgs@tongji.edu.cn — «信息反馈» на странице «О нас» 外事办公室. Личный ящик директора: yinwen@tongji.edu.cn. Сотрудник по России/Беларуси/Украине: Zhang Chuan (张川), zhangchuan@tongji.edu.cn; по Азии/Африке: Xu Li (徐俐), icyxu@tongji.edu.cn</t>
         </is>
       </c>
-      <c r="AH33" s="4" t="inlineStr">
+      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tongji.edu.cn/xxgk1/xrld1.htm
 • Https://fao.tongji.edu.cn/
@@ -11936,9 +11931,14 @@
 • Https://fao.tongji.edu.cn/gywm/bmgk.htm</t>
         </is>
       </c>
+      <c r="AH33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Zheng Qinghua (郑庆华)</t>
         </is>
       </c>
     </row>
@@ -12032,62 +12032,57 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>Wu Guosheng (吴国生)</t>
+          <t>QS2027: 296</t>
         </is>
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 296</t>
+          <t>THE2027: =196</t>
         </is>
       </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =196</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 10</t>
         </is>
       </c>
-      <c r="V34" s="4" t="n">
+      <c r="U34" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
-      <c r="Y34" s="4" t="inlineStr"/>
-      <c r="Z34" s="4" t="inlineStr">
+      <c r="Y34" s="4" t="inlineStr">
         <is>
           <t>• Space Manufacturing Research Institute (established March 2026)
 • Aerospace Manufacturing and Information Engineering Research Institute (2020)</t>
         </is>
       </c>
-      <c r="AA34" s="4" t="inlineStr">
+      <c r="Z34" s="4" t="inlineStr">
         <is>
           <t>• Lead university of the University Alliance of the Silk Road (UASR)
 • XJTU ultra-light alloy materials used on CAST micro-nano satellites launched 2016-12-22</t>
         </is>
       </c>
-      <c r="AB34" s="4" t="inlineStr"/>
-      <c r="AC34" s="4" t="n">
+      <c r="AA34" s="4" t="inlineStr"/>
+      <c r="AB34" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="AD34" s="6" t="inlineStr">
+      <c r="AC34" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE34" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF34" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>• Собственных КА нет; космическая тематика — материалы и космическое производство
 • Секретарь парткома У Гошэн с апреля 2026
@@ -12096,7 +12091,7 @@
 • Адресат: chenping@xjtu.edu.cn — контактный адрес отдела на англ. сайте (https://en.xjtu.edu.cn/2021-03/26/c_606770.htm); это ящик сотрудника Chen Ping, но его должность/китайское имя на официальных страницах не найдены. Поэтому адресат — начальник отдела. Официальный ящик канцелярии отдела: gjc@xjtu.edu.cn (Чжан Шаньшань, 处务办公室); личный e-mail начальника liuwenfeng@xjtu.edu.cn — рекомендуется в копию</t>
         </is>
       </c>
-      <c r="AH34" s="4" t="inlineStr">
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>• Https://www.xjtu.edu.cn/jdgk/xxld.htm
 • Https://en.xjtu.edu.cn/2021-03/26/c_606770.htm
@@ -12108,9 +12103,14 @@
 • Https://www.xjtu.edu.cn/gjjl/gjhzyjlc.htm</t>
         </is>
       </c>
+      <c r="AH34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Wu Guosheng (吴国生)</t>
         </is>
       </c>
     </row>
@@ -12204,61 +12204,56 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>Xu Bo (徐波)</t>
+          <t>QS2027: 416</t>
         </is>
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 416</t>
+          <t>THE2027: 351-375</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 351-375</t>
-        </is>
-      </c>
-      <c r="U35" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 66</t>
         </is>
       </c>
-      <c r="V35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
-      <c r="Y35" s="4" t="inlineStr"/>
+      <c r="Y35" s="4" t="inlineStr">
+        <is>
+          <t>Tiandu-Shenzhen University Deep Space Exploration Joint Laboratory (天都-深圳大学深空探测联合实验室, 2023)</t>
+        </is>
+      </c>
       <c r="Z35" s="4" t="inlineStr">
-        <is>
-          <t>Tiandu-Shenzhen University Deep Space Exploration Joint Laboratory (天都-深圳大学深空探测联合实验室, 2023)</t>
-        </is>
-      </c>
-      <c r="AA35" s="4" t="inlineStr">
         <is>
           <t>• Joint lab with Tiandu Laboratory (deep-space exploration)
 • Recipient of Chang'e-5 lunar samples (CNSA)</t>
         </is>
       </c>
-      <c r="AB35" s="4" t="inlineStr"/>
-      <c r="AC35" s="4" t="n">
+      <c r="AA35" s="4" t="inlineStr"/>
+      <c r="AB35" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="AD35" s="7" t="inlineStr">
+      <c r="AC35" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="AD35" s="4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
       <c r="AE35" s="4" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF35" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG35" s="4" t="inlineStr">
         <is>
           <t>• Президента нет: секретарь парткома Сюй Бо временно руководит административной работой
 • Собственных КА нет
@@ -12267,7 +12262,7 @@
 • Адресат: Ящик international@szu.edu.cn подтверждён на https://en.szu.edu.cn/Contact_us.htm («For visiting, cooperation…»). Сайт отдела io.szu.edu.cn закрыт анти-бот защитой; имя руководителя найдено только в новости другого вуза (окт. 2023) — может быть устаревшим. Безопаснее нейтральное обращение «Dear Director of the International Office,»</t>
         </is>
       </c>
-      <c r="AH35" s="4" t="inlineStr">
+      <c r="AG35" s="4" t="inlineStr">
         <is>
           <t>• Https://www.szu.edu.cn/xxgk/xrld.htm
 • Https://en.szu.edu.cn/Contact_us.htm
@@ -12279,9 +12274,14 @@
 • Https://news.gdufe.edu.cn/45757</t>
         </is>
       </c>
+      <c r="AH35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Xu Bo (徐波)</t>
         </is>
       </c>
     </row>
@@ -12379,57 +12379,52 @@
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>Zhong Denghua (钟登华)</t>
+          <t>QS2027: 477</t>
         </is>
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 477</t>
+          <t>THE2022: 601-800 (not listed in later editions)</t>
         </is>
       </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>THE2022: 601-800 (not listed in later editions)</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 24</t>
         </is>
       </c>
-      <c r="V36" s="4" t="n">
+      <c r="U36" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V36" s="4" t="inlineStr"/>
       <c r="W36" s="4" t="inlineStr"/>
       <c r="X36" s="4" t="inlineStr"/>
-      <c r="Y36" s="4" t="inlineStr"/>
-      <c r="Z36" s="4" t="inlineStr">
+      <c r="Y36" s="4" t="inlineStr">
         <is>
           <t>• College of Land Science and Technology (土地科学与技术学院, agricultural remote sensing)
 • College of Resources and Environmental Sciences</t>
         </is>
       </c>
+      <c r="Z36" s="4" t="inlineStr"/>
       <c r="AA36" s="4" t="inlineStr"/>
-      <c r="AB36" s="4" t="inlineStr"/>
-      <c r="AC36" s="4" t="n">
+      <c r="AB36" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AD36" s="7" t="inlineStr">
+      <c r="AC36" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="AD36" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE36" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF36" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>• Собственных КА нет; потенциальный потребитель данных ДЗЗ для сельского хозяйства
 • Последний рейтинг THE — 2022
@@ -12437,7 +12432,7 @@
 • Адресат: oice@cau.edu.cn закреплён за Zhang Ruyu (Европа). Начальник управления — Tang Ying (唐莹), tangying@cau.edu.cn (https://global.cau.edu.cn/col/col52260/index.html); отдел курирует зам. начальника Wu Jian (吴健), jianwu@cau.edu.cn. Для Азии/Африки — Chang Xin (常鑫), internationaloffice@cau.edu.cn; Америка — Su Hetong (苏鹤童), oirf@cau.edu.cn. Пол Zhang Ruyu не указан. Официальное приглашение лучше адресовать начальнику («Dear Director Tang,»), отправив на oice@ с копией tangying@</t>
         </is>
       </c>
-      <c r="AH36" s="4" t="inlineStr">
+      <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cau.edu.cn/xxgk/xxld/index.htm
 • Https://en.cau.edu.cn/col/col32357/index.html
@@ -12450,9 +12445,14 @@
 • Https://global.cau.edu.cn/col/col52636/index.html</t>
         </is>
       </c>
+      <c r="AH36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Zhong Denghua (钟登华)</t>
         </is>
       </c>
     </row>
@@ -12546,65 +12546,60 @@
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>Wang Shuxin (王树新)</t>
+          <t>QS2027: 465</t>
         </is>
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 465</t>
+          <t>THE2027: 376-400</t>
         </is>
       </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 376-400</t>
-        </is>
-      </c>
-      <c r="U37" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 34</t>
         </is>
       </c>
-      <c r="V37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="inlineStr"/>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
-      <c r="Z37" s="4" t="inlineStr"/>
-      <c r="AA37" s="4" t="inlineStr">
+      <c r="Z37" s="4" t="inlineStr">
         <is>
           <t>• Led the Chang'e-4 biological science payload (lunar mini-biosphere, 2018-12-08 launch
 • CNSA lunar programme)
 • Shennong Kaiwu-2 (神农开物2号) space ecosystem payload flown on Kuaizhou-11 Y8</t>
         </is>
       </c>
-      <c r="AB37" s="4" t="inlineStr"/>
-      <c r="AC37" s="4" t="n">
+      <c r="AA37" s="4" t="inlineStr"/>
+      <c r="AB37" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AD37" s="7" t="inlineStr">
+      <c r="AC37" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="AD37" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE37" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF37" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG37" s="4" t="inlineStr">
         <is>
           <t>• Собственных КА нет; полезные нагрузки: биосфера Chang'e-4, Shennong Kaiwu-2
 • Международные e-mail и телефон — из результатов поиска (сайт блокирует запросы); проверить перед использованием
 • Адресат: Сайт отдела intex.cqu.edu.cn и англ. сайт закрыты анти-бот защитой (HTTP 412); имя подтверждено новостью на www.cqu.edu.cn от 19.12.2025. Привязка global@cqu.edu.cn к Office of International Affairs — только по поисковой выдаче (english.cqu.edu.cn Contact Us), открыть страницу не удалось</t>
         </is>
       </c>
-      <c r="AH37" s="4" t="inlineStr">
+      <c r="AG37" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cqu.edu.cn/xqgk/xrld.htm
 • Https://www.cqu.edu.cn/
@@ -12616,9 +12611,14 @@
 • Https://www.cqu.edu.cn/info/1111/64301.htm</t>
         </is>
       </c>
+      <c r="AH37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Wang Shuxin (王树新)</t>
         </is>
       </c>
     </row>
@@ -12710,60 +12710,55 @@
           <t>President</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr">
-        <is>
-          <t>Zhang Xiaoyong (张晓永)</t>
-        </is>
-      </c>
+      <c r="R38" s="4" t="inlineStr"/>
       <c r="S38" s="4" t="inlineStr"/>
-      <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="inlineStr">
+      <c r="T38" s="4" t="inlineStr">
         <is>
           <t>BCUR2026: 144</t>
         </is>
       </c>
-      <c r="V38" s="4" t="n">
+      <c r="U38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="4" t="inlineStr">
+      <c r="V38" s="4" t="inlineStr">
         <is>
           <t>• Zhongbei Daxue-1 (中北大学一号, 6U
 • Launched 2025-11-10 on Ceres-1 Y19, launch failure, did not reach orbit)</t>
         </is>
       </c>
-      <c r="X38" s="4" t="inlineStr">
+      <c r="W38" s="4" t="inlineStr">
         <is>
           <t>• NUC-Taihang Constellation (中北大学-太行星座): 128 intelligent satellites
 • Phase 1 has 6 satellites by end-2027, 18 more by 2029, 36 by 2031, the rest by 2035</t>
         </is>
       </c>
+      <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
-      <c r="Z38" s="4" t="inlineStr"/>
-      <c r="AA38" s="4" t="inlineStr">
+      <c r="Z38" s="4" t="inlineStr">
         <is>
           <t>Taihang Constellation with Orienspace (东方空间技术(山东)有限公司) and Beijing Maiya Technology (北京劢亚科技)</t>
         </is>
       </c>
-      <c r="AB38" s="4" t="inlineStr"/>
-      <c r="AC38" s="4" t="n">
+      <c r="AA38" s="4" t="inlineStr"/>
+      <c r="AB38" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AD38" s="7" t="inlineStr">
+      <c r="AC38" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="AD38" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE38" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF38" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG38" s="4" t="inlineStr">
         <is>
           <t>• Оборонная специализация; спутники Taihang — двойного назначения (по nanosats.eu)
 • Первый КА Zhongbei Daxue-1 потерян при аварии РН 10.11.2025 — на орбите 0
@@ -12772,7 +12767,7 @@
 • Адресат: Fan Peng — не директор (как было указано во входных данных), а начальник сектора; китайское написание имени не подтверждено. Англ. страница, вероятно, устарела: на актуальной китайской странице (https://international.nuc.edu.cn/xyjs/lxfs.htm) Fan Peng отсутствует, начальник сектора межд. обменов — Han Ying (韩英, hanying@nuc.edu.cn), а руководитель — Zhao Yuhong (赵宇宏), декан Колледжа международного образования / начальник Департамента международного обмена и сотрудничества (国际交流合作部部长). Рекомендуется адресовать Zhao Yuhong («Dear Dean Zhao,») с копией fanpeng@ и hanying@</t>
         </is>
       </c>
-      <c r="AH38" s="4" t="inlineStr">
+      <c r="AG38" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nuc.edu.cn/xxgk/xrld.htm
 • Https://international.nuc.edu.cn/gjhzjlc_e/Contact_Us.htm
@@ -12784,9 +12779,14 @@
 • Https://www.timeshighereducation.com/world-university-rankings/latest/world-ranking</t>
         </is>
       </c>
+      <c r="AH38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Zhang Xiaoyong (张晓永)</t>
         </is>
       </c>
     </row>
@@ -12884,58 +12884,53 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>Wu Xiaocheng (邬小撑)</t>
+          <t>QS2027: 335</t>
         </is>
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 335</t>
+          <t>THE2027: =247</t>
         </is>
       </c>
       <c r="T39" s="4" t="inlineStr">
         <is>
-          <t>THE2027: =247</t>
-        </is>
-      </c>
-      <c r="U39" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 15</t>
         </is>
       </c>
-      <c r="V39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="inlineStr"/>
       <c r="X39" s="4" t="inlineStr"/>
-      <c r="Y39" s="4" t="inlineStr"/>
-      <c r="Z39" s="4" t="inlineStr">
+      <c r="Y39" s="4" t="inlineStr">
         <is>
           <t>• School of Information Science and Engineering
 • School of Instrument Science and Engineering (仪器科学与工程学院)
 • School of Cyber Science and Engineering (no dedicated aerospace school found)</t>
         </is>
       </c>
+      <c r="Z39" s="4" t="inlineStr"/>
       <c r="AA39" s="4" t="inlineStr"/>
-      <c r="AB39" s="4" t="inlineStr"/>
-      <c r="AC39" s="4" t="n">
+      <c r="AB39" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AD39" s="6" t="inlineStr">
+      <c r="AC39" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="AD39" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE39" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF39" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>• Собственных КА нет (участие в оборудовании Shenzhou/Tiangong)
 • Отдел международного сотрудничества указывает только телефоны
@@ -12943,7 +12938,7 @@
 • Адресат: cis@pub.seu.edu.cn — ящик Центра иностранных студентов (Колледж зарубежного образования), не для партнёрств; на странице «联系我们» OIC (https://oic.seu.edu.cn/lxwm_69042/list.htm) для международного сотрудничества указан globalseu@pub.seu.edu.cn. Должность Ye Zhirui подтверждена профилем на сайте School of Transportation (страница 2019 г.; на сайте OIC страницы руководства нет) — может быть устаревшей</t>
         </is>
       </c>
-      <c r="AH39" s="4" t="inlineStr">
+      <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>• Https://www.seu.edu.cn/28446/list.htm
 • Https://oic.seu.edu.cn/18926/list.htm
@@ -12957,9 +12952,14 @@
 • Https://tc.seu.edu.cn/2019/1022/c25722a291865/page.htm</t>
         </is>
       </c>
+      <c r="AH39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Wu Xiaocheng (邬小撑)</t>
         </is>
       </c>
     </row>
@@ -13057,53 +13057,48 @@
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>Yang Guishan (杨桂山)</t>
-        </is>
-      </c>
-      <c r="S40" s="4" t="inlineStr">
-        <is>
           <t>QS2027: 1001-1200</t>
         </is>
       </c>
-      <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr">
+      <c r="S40" s="4" t="inlineStr"/>
+      <c r="T40" s="4" t="inlineStr">
         <is>
           <t>BCUR2026: 63</t>
         </is>
       </c>
-      <c r="V40" s="4" t="n">
+      <c r="U40" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V40" s="4" t="inlineStr"/>
       <c r="W40" s="4" t="inlineStr"/>
       <c r="X40" s="4" t="inlineStr"/>
-      <c r="Y40" s="4" t="inlineStr"/>
-      <c r="Z40" s="4" t="inlineStr">
+      <c r="Y40" s="4" t="inlineStr">
         <is>
           <t>• School of Geography and Remote Sensing (地理与遥感学院)
 • College of Information Science and Engineering</t>
         </is>
       </c>
+      <c r="Z40" s="4" t="inlineStr"/>
       <c r="AA40" s="4" t="inlineStr"/>
-      <c r="AB40" s="4" t="inlineStr"/>
-      <c r="AC40" s="4" t="n">
+      <c r="AB40" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AD40" s="6" t="inlineStr">
+      <c r="AC40" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="AD40" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE40" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF40" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG40" s="4" t="inlineStr">
         <is>
           <t>• Собственных КА нет; профиль — водные ресурсы, гидрология, ДЗЗ-приложения
 • Нет в рейтинге THE
@@ -13111,7 +13106,7 @@
 • Адресат: Internationalexchange@hhu.edu.cn подтверждён на https://en.hhu.edu.cn/341/list.htm как ящик International Exchange Office. Общий ящик управления: gjhzc@hhu.edu.cn (можно в копию). На сайте управления нет страницы руководства; имя — из новости апреля 2025 г. (зам. начальника — Wu Yao 吴瑶)</t>
         </is>
       </c>
-      <c r="AH40" s="4" t="inlineStr">
+      <c r="AG40" s="4" t="inlineStr">
         <is>
           <t>• Https://www.hhu.edu.cn/xrld_23325/list.htm
 • Https://en.hhu.edu.cn/341/list.htm
@@ -13124,9 +13119,14 @@
 • Https://sdxy.hhu.edu.cn/_t947/2025/0427/c5763a301995/page.htm</t>
         </is>
       </c>
+      <c r="AH40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Yang Guishan (杨桂山)</t>
         </is>
       </c>
     </row>
@@ -13220,57 +13220,52 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>Song Yingdong (宋迎东)</t>
+          <t>QS2027: 1001-1200</t>
         </is>
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 1001-1200</t>
+          <t>THE2027: 651-700</t>
         </is>
       </c>
       <c r="T41" s="4" t="inlineStr">
         <is>
-          <t>THE2027: 651-700</t>
-        </is>
-      </c>
-      <c r="U41" s="4" t="inlineStr">
-        <is>
           <t>BCUR2026: 43</t>
         </is>
       </c>
-      <c r="V41" s="4" t="n">
+      <c r="U41" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="inlineStr"/>
       <c r="X41" s="4" t="inlineStr"/>
       <c r="Y41" s="4" t="inlineStr"/>
       <c r="Z41" s="4" t="inlineStr"/>
-      <c r="AA41" s="4" t="inlineStr"/>
-      <c r="AB41" s="4" t="inlineStr">
+      <c r="AA41" s="4" t="inlineStr">
         <is>
           <t>Entity List США (с May 2020)
 «Семь сыновей национальной обороны»</t>
         </is>
       </c>
-      <c r="AC41" s="4" t="n">
+      <c r="AB41" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="AD41" s="7" t="inlineStr">
+      <c r="AC41" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="AD41" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE41" s="4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF41" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG41" s="4" t="inlineStr">
         <is>
           <t>• Страница руководства обновлена в июне 2026
 • Телефон — коммутатор; международный отдел (студенты) +86-451-82568266
@@ -13279,7 +13274,7 @@
 • Адресат: На странице состава отдела heufao@hrbeu.edu.cn указан как контакт Инь Хуа (尹华), руководителя Офиса по иностранным студентам (набор и обучение иностранных студентов), так что ящик, вероятно, читает этот офис. Рекомендуем поставить в копию начальника douzheng@hrbeu.edu.cn. Замначальника отдела Дин Синь (丁昕, dingxin-2019@hrbeu.edu.cn) курирует русскоязычные страны, а Лю Сыцзя (刘思嘉, liusijia@hrbeu.edu.cn) — нерусскоязычные</t>
         </is>
       </c>
-      <c r="AH41" s="4" t="inlineStr">
+      <c r="AG41" s="4" t="inlineStr">
         <is>
           <t>• Https://www.hrbeu.edu.cn/xxgk/xrld1.htm
 • Https://www.hrbeu.edu.cn/
@@ -13294,9 +13289,14 @@
 • Https://fao.hrbeu.edu.cn/4775/list.htm</t>
         </is>
       </c>
+      <c r="AH41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="AI41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>Song Yingdong (宋迎东)</t>
         </is>
       </c>
     </row>
